--- a/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_45.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_18_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5200641.094333326</v>
+        <v>5200763.034235172</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13726352.19588476</v>
+        <v>13726352.1958848</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13726352.19588476</v>
+        <v>13726352.1958848</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1662692.662948964</v>
+        <v>1662692.662948989</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1662692.662948964</v>
+        <v>1662692.662948989</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41813837.40841836</v>
+        <v>41813837.40841834</v>
       </c>
     </row>
   </sheetData>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.82316218912671</v>
+        <v>76.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>44.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>5.339155739849787</v>
@@ -708,7 +708,7 @@
         <v>80.87057986262442</v>
       </c>
       <c r="T2" t="n">
-        <v>179.9509787134886</v>
+        <v>160.2494061900346</v>
       </c>
       <c r="U2" t="n">
         <v>244.189778960671</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5287434221972</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -781,19 +781,19 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R3" t="n">
-        <v>129.1861746508698</v>
+        <v>340</v>
       </c>
       <c r="S3" t="n">
-        <v>340</v>
+        <v>246.156074917163</v>
       </c>
       <c r="T3" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>112.0093108800105</v>
+        <v>9.510667191520156</v>
       </c>
       <c r="W3" t="n">
         <v>27.37314290982852</v>
@@ -973,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5287434221972</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1018,25 +1018,25 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R6" t="n">
-        <v>129.1861746508698</v>
+        <v>340</v>
       </c>
       <c r="S6" t="n">
         <v>57.64862260612074</v>
       </c>
       <c r="T6" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>278.7007835732297</v>
+        <v>9.510667191520156</v>
       </c>
       <c r="W6" t="n">
         <v>27.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>14.86273944538755</v>
+        <v>58.76777390016417</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>313.5601839382404</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>330.1322758656664</v>
       </c>
       <c r="I9" t="n">
-        <v>209.8688387215372</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R9" t="n">
-        <v>357</v>
+        <v>129.1861746508698</v>
       </c>
       <c r="S9" t="n">
-        <v>290.5261424736938</v>
+        <v>57.64862260612074</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>14.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -1371,19 +1371,19 @@
         <v>91.47457824299391</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>52.33915573984979</v>
       </c>
       <c r="E11" t="n">
         <v>46.36328960686865</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>46.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>45.36340243776998</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>45.97491498493444</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1419,13 +1419,13 @@
         <v>127.8705798626244</v>
       </c>
       <c r="T11" t="n">
-        <v>226.9509787134885</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>291.189778960671</v>
+        <v>187.6483953370019</v>
       </c>
       <c r="V11" t="n">
-        <v>13.39217221622717</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>280.3734759809475</v>
@@ -1434,7 +1434,7 @@
         <v>234.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>153.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>292.5754424659179</v>
+        <v>370.0000000000156</v>
       </c>
       <c r="S12" t="n">
         <v>104.6486226061207</v>
@@ -1501,7 +1501,7 @@
         <v>46.50812370807985</v>
       </c>
       <c r="U12" t="n">
-        <v>42.19649183565845</v>
+        <v>110.9437276939145</v>
       </c>
       <c r="V12" t="n">
         <v>56.51066719152016</v>
@@ -1565,13 +1565,13 @@
         <v>257.4668099806543</v>
       </c>
       <c r="P13" t="n">
-        <v>308.0742579840152</v>
+        <v>104.3862020921092</v>
       </c>
       <c r="Q13" t="n">
         <v>353.041266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>156.9680393023725</v>
+        <v>360.6560951942658</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>25.33915573984979</v>
       </c>
       <c r="E14" t="n">
-        <v>19.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>19.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>18.36340243776998</v>
       </c>
       <c r="H14" t="n">
-        <v>12.94590963221694</v>
+        <v>18.97491498493444</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>100.8705798626244</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>199.9509787134885</v>
       </c>
       <c r="U14" t="n">
         <v>264.189778960671</v>
@@ -1665,7 +1665,7 @@
         <v>244.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>253.3734759809475</v>
+        <v>68.28300779184656</v>
       </c>
       <c r="X14" t="n">
         <v>207.2818334606677</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1729,25 +1729,25 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>370.0000000000169</v>
+        <v>149.1861746508699</v>
       </c>
       <c r="S15" t="n">
-        <v>77.64862260612074</v>
+        <v>370.0000000000175</v>
       </c>
       <c r="T15" t="n">
-        <v>370.0000000000073</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="U15" t="n">
-        <v>152.4731927431642</v>
+        <v>15.19649183565845</v>
       </c>
       <c r="V15" t="n">
         <v>29.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>47.37314290982852</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="X15" t="n">
-        <v>34.86273944538755</v>
+        <v>117.6112735558358</v>
       </c>
       <c r="Y15" t="n">
         <v>14.39139276613435</v>
@@ -1808,7 +1808,7 @@
         <v>326.041266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>331.2420281158821</v>
+        <v>331.2420281158768</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>2.363402437769979</v>
       </c>
       <c r="H17" t="n">
-        <v>2.631528480965681</v>
+        <v>2.631528480952882</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>133.1861746508699</v>
@@ -1972,22 +1972,22 @@
         <v>61.64862260612073</v>
       </c>
       <c r="T18" t="n">
-        <v>300.0429473584373</v>
+        <v>3.508123708079854</v>
       </c>
       <c r="U18" t="n">
-        <v>370.0000000000074</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>13.51066719152016</v>
+        <v>127.5530790349583</v>
       </c>
       <c r="W18" t="n">
-        <v>31.37314290982852</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="X18" t="n">
-        <v>18.86273944538755</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>370.0000000000075</v>
       </c>
     </row>
     <row r="19">
@@ -2091,10 +2091,10 @@
         <v>3.889628708011855</v>
       </c>
       <c r="G20" t="n">
-        <v>2.363402437769979</v>
+        <v>2.363402437769992</v>
       </c>
       <c r="H20" t="n">
-        <v>2.974914984934444</v>
+        <v>2.974914984934458</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>84.52719335864266</v>
+        <v>84.52719335864288</v>
       </c>
       <c r="T20" t="n">
-        <v>183.9509787134885</v>
+        <v>183.9509787134886</v>
       </c>
       <c r="U20" t="n">
         <v>248.189778960671</v>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2200,28 +2200,28 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R21" t="n">
-        <v>133.1861746508699</v>
+        <v>133.1861746508698</v>
       </c>
       <c r="S21" t="n">
-        <v>61.64862260612073</v>
+        <v>61.64862260612074</v>
       </c>
       <c r="T21" t="n">
-        <v>285.1374749150103</v>
+        <v>113.6474277193134</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>13.51066719152016</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="W21" t="n">
         <v>31.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>18.86273944538755</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>91.92974255009086</v>
+        <v>91.92974255009085</v>
       </c>
       <c r="N22" t="n">
         <v>143.1418949438161</v>
@@ -2328,10 +2328,10 @@
         <v>3.889628708011855</v>
       </c>
       <c r="G23" t="n">
-        <v>2.363402437769992</v>
+        <v>2.363402437769979</v>
       </c>
       <c r="H23" t="n">
-        <v>2.974914984934458</v>
+        <v>2.631528480952882</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>84.52719335865527</v>
+        <v>84.87057986262441</v>
       </c>
       <c r="T23" t="n">
-        <v>183.9509787134886</v>
+        <v>183.9509787134885</v>
       </c>
       <c r="U23" t="n">
         <v>248.189778960671</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>370.0000000000077</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>100.0345198208048</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>143.5605030307649</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>133.1861746508698</v>
+        <v>133.1861746508699</v>
       </c>
       <c r="S24" t="n">
-        <v>61.64862260612074</v>
+        <v>61.64862260612073</v>
       </c>
       <c r="T24" t="n">
-        <v>3.508123708079836</v>
+        <v>3.508123708079854</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>91.92974255009085</v>
+        <v>91.92974255009086</v>
       </c>
       <c r="N25" t="n">
         <v>143.1418949438161</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>137.4745782429939</v>
       </c>
       <c r="D26" t="n">
         <v>98.33915573984979</v>
@@ -2565,7 +2565,7 @@
         <v>92.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>91.36340243776998</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>91.97491498493444</v>
@@ -2601,19 +2601,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>173.8705798626244</v>
       </c>
       <c r="T26" t="n">
         <v>272.9509787134885</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>37.87704997446469</v>
       </c>
       <c r="V26" t="n">
         <v>317.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>257.8588056423724</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>18.13227586566641</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>96.35033004925936</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>96.35033004931834</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>222.1861746508699</v>
@@ -2741,22 +2741,22 @@
         <v>85.27398881351688</v>
       </c>
       <c r="M28" t="n">
-        <v>180.9297425500909</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>160.2779970747116</v>
       </c>
       <c r="P28" t="n">
-        <v>318.3482545246057</v>
+        <v>339.000000000011</v>
       </c>
       <c r="Q28" t="n">
-        <v>339.0000000000242</v>
+        <v>339.000000000011</v>
       </c>
       <c r="R28" t="n">
-        <v>339.0000000000242</v>
+        <v>339.000000000011</v>
       </c>
       <c r="S28" t="n">
         <v>47.29370921105216</v>
@@ -2790,22 +2790,22 @@
         <v>169.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>137.4745782429939</v>
       </c>
       <c r="D29" t="n">
         <v>98.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>92.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>92.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>91.36340243776998</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>91.97491498493444</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,16 +2844,16 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>337.189778960671</v>
       </c>
       <c r="V29" t="n">
-        <v>317.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>249.8024409943414</v>
+        <v>4.679705680576266</v>
       </c>
       <c r="X29" t="n">
-        <v>280.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>199.3174326828064</v>
@@ -2872,7 +2872,7 @@
         <v>49.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>132.2880169469653</v>
+        <v>35.93768689770263</v>
       </c>
       <c r="E30" t="n">
         <v>30.67209722191262</v>
@@ -2920,7 +2920,7 @@
         <v>150.6486226061207</v>
       </c>
       <c r="T30" t="n">
-        <v>92.50812370807985</v>
+        <v>188.8584537573356</v>
       </c>
       <c r="U30" t="n">
         <v>88.19649183565845</v>
@@ -2975,25 +2975,25 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>85.27398881351688</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>232.1418949438161</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>303.4668099806543</v>
       </c>
       <c r="P31" t="n">
-        <v>339.0000000000138</v>
+        <v>328.378885118641</v>
       </c>
       <c r="Q31" t="n">
-        <v>339.0000000000138</v>
+        <v>339.0000000000092</v>
       </c>
       <c r="R31" t="n">
-        <v>10.96300136129877</v>
+        <v>339.0000000000092</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>60.30791792904022</v>
+        <v>62.99931295557451</v>
       </c>
       <c r="C32" t="n">
         <v>30.47457824299391</v>
@@ -3078,7 +3078,7 @@
         <v>66.87057986262441</v>
       </c>
       <c r="T32" t="n">
-        <v>165.9509787134885</v>
+        <v>163.2595836869416</v>
       </c>
       <c r="U32" t="n">
         <v>230.189778960671</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>209.8688387215372</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3151,13 +3151,13 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R33" t="n">
-        <v>322.0000000000164</v>
+        <v>124.0726636978166</v>
       </c>
       <c r="S33" t="n">
-        <v>235.341085530911</v>
+        <v>322.0000000000132</v>
       </c>
       <c r="T33" t="n">
-        <v>322.0000000000164</v>
+        <v>322.0000000000132</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>13.37314290982852</v>
       </c>
       <c r="X33" t="n">
-        <v>0.8627394453875468</v>
+        <v>322.0000000000132</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8582049734021453</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,13 +3309,13 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.8582049734021348</v>
       </c>
       <c r="S35" t="n">
-        <v>60.87057986262441</v>
+        <v>60.87057986262442</v>
       </c>
       <c r="T35" t="n">
-        <v>159.9509787134885</v>
+        <v>159.9509787134886</v>
       </c>
       <c r="U35" t="n">
         <v>224.189778960671</v>
@@ -3343,22 +3343,22 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>309</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>309</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>70.91862771927721</v>
       </c>
       <c r="I36" t="n">
         <v>209.8688387215372</v>
@@ -3388,10 +3388,10 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R36" t="n">
-        <v>109.1861746508699</v>
+        <v>187.4779452799755</v>
       </c>
       <c r="S36" t="n">
-        <v>37.64862260612073</v>
+        <v>37.64862260612074</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>7.373142909828516</v>
+        <v>309</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>67.92974255009086</v>
+        <v>67.92974255009085</v>
       </c>
       <c r="N37" t="n">
         <v>119.1418949438161</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.8582049734021348</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>60.87057986262441</v>
@@ -3555,7 +3555,7 @@
         <v>159.9509787134885</v>
       </c>
       <c r="U38" t="n">
-        <v>224.189778960671</v>
+        <v>225.0479839340731</v>
       </c>
       <c r="V38" t="n">
         <v>204.8510241668239</v>
@@ -3580,16 +3580,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
         <v>309</v>
       </c>
-      <c r="D39" t="n">
-        <v>280.7874664408144</v>
-      </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>118.622263697805</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R39" t="n">
-        <v>109.1861746508699</v>
+        <v>309</v>
       </c>
       <c r="S39" t="n">
-        <v>37.64862260612073</v>
+        <v>309</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -3735,19 +3735,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>168.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>97.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>91.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>91.88962870801186</v>
+        <v>90.82888257711261</v>
       </c>
       <c r="G41" t="n">
         <v>90.36340243776998</v>
@@ -3792,19 +3792,19 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>309.0000000000633</v>
       </c>
       <c r="V41" t="n">
-        <v>309.00000000006</v>
+        <v>309.0000000000598</v>
       </c>
       <c r="W41" t="n">
-        <v>60.92006288412443</v>
+        <v>309.0000000000598</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>198.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>84.27398881351688</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>179.9297425500909</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>231.1418949438161</v>
@@ -3935,16 +3935,16 @@
         <v>302.4668099806543</v>
       </c>
       <c r="P43" t="n">
-        <v>309.0000000001155</v>
+        <v>309.0000000001262</v>
       </c>
       <c r="Q43" t="n">
-        <v>46.06105450075427</v>
+        <v>309.000000000126</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>47.55849507527741</v>
       </c>
       <c r="S43" t="n">
-        <v>46.29370921105216</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3978,19 +3978,19 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>124.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>118.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>118.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>117.36340243777</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>117.9749149849345</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4026,19 +4026,19 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>298.9509787134886</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>303.2858298090766</v>
+        <v>309.0000000000542</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>309.0000000000516</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>274.8853665392265</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>306.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>39.52874342219718</v>
       </c>
       <c r="H45" t="n">
-        <v>44.13227586566643</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>148.623866751577</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>58.89340317185593</v>
       </c>
       <c r="T45" t="n">
         <v>118.5081237080798</v>
@@ -4117,7 +4117,7 @@
         <v>146.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>133.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>113.3913927661343</v>
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>111.2739888135169</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>258.1418949438161</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>309.0000000001208</v>
+        <v>102.0842251125931</v>
       </c>
       <c r="P46" t="n">
-        <v>309.000000000119</v>
+        <v>309.000000000138</v>
       </c>
       <c r="Q46" t="n">
-        <v>28.51002819338653</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>309.0000000001422</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>73.29370921105215</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77.51690301297344</v>
+        <v>32.59308660590887</v>
       </c>
       <c r="C2" t="n">
         <v>32.59308660590887</v>
@@ -4321,25 +4321,25 @@
         <v>27.2</v>
       </c>
       <c r="J2" t="n">
-        <v>27.2</v>
+        <v>363.8</v>
       </c>
       <c r="K2" t="n">
-        <v>232.8476832091187</v>
+        <v>413.4132977889448</v>
       </c>
       <c r="L2" t="n">
-        <v>294.3973662241941</v>
+        <v>474.9629808040201</v>
       </c>
       <c r="M2" t="n">
-        <v>630.9973662241941</v>
+        <v>811.5629808040202</v>
       </c>
       <c r="N2" t="n">
-        <v>967.5973662241942</v>
+        <v>1148.16298080402</v>
       </c>
       <c r="O2" t="n">
-        <v>967.5973662241942</v>
+        <v>1148.16298080402</v>
       </c>
       <c r="P2" t="n">
-        <v>1023.4</v>
+        <v>1203.965614579826</v>
       </c>
       <c r="Q2" t="n">
         <v>1360</v>
@@ -4351,22 +4351,22 @@
         <v>1278.312545593309</v>
       </c>
       <c r="T2" t="n">
-        <v>1096.543880226149</v>
+        <v>1116.444458532668</v>
       </c>
       <c r="U2" t="n">
-        <v>849.8875378416324</v>
+        <v>869.7881161481514</v>
       </c>
       <c r="V2" t="n">
-        <v>622.7652912084769</v>
+        <v>642.665869514996</v>
       </c>
       <c r="W2" t="n">
-        <v>387.0345073893379</v>
+        <v>406.935085695857</v>
       </c>
       <c r="X2" t="n">
-        <v>197.8609382371483</v>
+        <v>217.7615165436674</v>
       </c>
       <c r="Y2" t="n">
-        <v>90.46959209289942</v>
+        <v>110.3701703994185</v>
       </c>
     </row>
     <row r="3">
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>239.1887259813507</v>
+        <v>568.0056385290246</v>
       </c>
       <c r="C3" t="n">
-        <v>239.1887259813507</v>
+        <v>568.0056385290246</v>
       </c>
       <c r="D3" t="n">
-        <v>239.1887259813507</v>
+        <v>568.0056385290246</v>
       </c>
       <c r="E3" t="n">
-        <v>239.1887259813507</v>
+        <v>568.0056385290246</v>
       </c>
       <c r="F3" t="n">
-        <v>239.1887259813507</v>
+        <v>568.0056385290246</v>
       </c>
       <c r="G3" t="n">
         <v>239.1887259813507</v>
@@ -4403,19 +4403,19 @@
         <v>170.8726316847329</v>
       </c>
       <c r="K3" t="n">
-        <v>393.7634226847767</v>
+        <v>275.7536123162412</v>
       </c>
       <c r="L3" t="n">
-        <v>710.4249701290335</v>
+        <v>592.4151597604979</v>
       </c>
       <c r="M3" t="n">
-        <v>849.3814118718926</v>
+        <v>731.3716015033571</v>
       </c>
       <c r="N3" t="n">
-        <v>1036.93706421531</v>
+        <v>918.9272538467744</v>
       </c>
       <c r="O3" t="n">
-        <v>1325.630873823557</v>
+        <v>1207.621063455022</v>
       </c>
       <c r="P3" t="n">
         <v>1360</v>
@@ -4424,28 +4424,28 @@
         <v>1212.351723846095</v>
       </c>
       <c r="R3" t="n">
-        <v>1081.860638340165</v>
+        <v>868.9173804117511</v>
       </c>
       <c r="S3" t="n">
-        <v>738.426294905822</v>
+        <v>620.2748804954248</v>
       </c>
       <c r="T3" t="n">
-        <v>394.9919514714786</v>
+        <v>620.2748804954248</v>
       </c>
       <c r="U3" t="n">
-        <v>394.9919514714786</v>
+        <v>620.2748804954248</v>
       </c>
       <c r="V3" t="n">
-        <v>281.8512334108619</v>
+        <v>610.6681459585358</v>
       </c>
       <c r="W3" t="n">
-        <v>254.2015941080048</v>
+        <v>583.0185066556787</v>
       </c>
       <c r="X3" t="n">
-        <v>239.1887259813507</v>
+        <v>568.0056385290246</v>
       </c>
       <c r="Y3" t="n">
-        <v>239.1887259813507</v>
+        <v>568.0056385290246</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>994.1926953529421</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="C4" t="n">
-        <v>1125.144701171378</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="D4" t="n">
-        <v>1243.413845296378</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="E4" t="n">
-        <v>1351.177579307644</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="F4" t="n">
-        <v>1351.177579307644</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="G4" t="n">
-        <v>1351.177579307644</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="H4" t="n">
-        <v>1351.177579307644</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="I4" t="n">
-        <v>1351.177579307644</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="J4" t="n">
-        <v>1351.177579307644</v>
+        <v>1215.536660124875</v>
       </c>
       <c r="K4" t="n">
         <v>1351.177579307644</v>
@@ -4518,13 +4518,13 @@
         <v>721.5045666624565</v>
       </c>
       <c r="W4" t="n">
-        <v>721.5045666624565</v>
+        <v>898.3454849221339</v>
       </c>
       <c r="X4" t="n">
-        <v>877.48535768665</v>
+        <v>1054.326275946327</v>
       </c>
       <c r="Y4" t="n">
-        <v>877.48535768665</v>
+        <v>1170.68557662536</v>
       </c>
     </row>
     <row r="5">
@@ -4561,22 +4561,22 @@
         <v>27.2</v>
       </c>
       <c r="K5" t="n">
+        <v>76.81329778894472</v>
+      </c>
+      <c r="L5" t="n">
         <v>294.3973662241941</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>630.9973662241941</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>967.5973662241942</v>
       </c>
-      <c r="N5" t="n">
-        <v>1304.197366224194</v>
-      </c>
       <c r="O5" t="n">
-        <v>1304.197366224194</v>
+        <v>967.5973662241942</v>
       </c>
       <c r="P5" t="n">
-        <v>1360</v>
+        <v>1023.4</v>
       </c>
       <c r="Q5" t="n">
         <v>1360</v>
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>356.0169125476739</v>
+        <v>714.0686868686869</v>
       </c>
       <c r="C6" t="n">
-        <v>356.0169125476739</v>
+        <v>370.6343434343435</v>
       </c>
       <c r="D6" t="n">
-        <v>356.0169125476739</v>
+        <v>27.2</v>
       </c>
       <c r="E6" t="n">
-        <v>356.0169125476739</v>
+        <v>27.2</v>
       </c>
       <c r="F6" t="n">
-        <v>356.0169125476739</v>
+        <v>27.2</v>
       </c>
       <c r="G6" t="n">
         <v>27.2</v>
@@ -4640,19 +4640,19 @@
         <v>170.8726316847329</v>
       </c>
       <c r="K6" t="n">
-        <v>275.7536123162412</v>
+        <v>393.7634226847767</v>
       </c>
       <c r="L6" t="n">
-        <v>592.4151597604979</v>
+        <v>710.4249701290335</v>
       </c>
       <c r="M6" t="n">
-        <v>731.3716015033571</v>
+        <v>849.3814118718926</v>
       </c>
       <c r="N6" t="n">
-        <v>918.9272538467744</v>
+        <v>1036.93706421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1207.621063455022</v>
+        <v>1325.630873823557</v>
       </c>
       <c r="P6" t="n">
         <v>1360</v>
@@ -4661,28 +4661,28 @@
         <v>1212.351723846095</v>
       </c>
       <c r="R6" t="n">
-        <v>1081.860638340165</v>
+        <v>868.9173804117511</v>
       </c>
       <c r="S6" t="n">
-        <v>1023.629706414791</v>
+        <v>810.6864484863765</v>
       </c>
       <c r="T6" t="n">
-        <v>680.1953629804475</v>
+        <v>810.6864484863765</v>
       </c>
       <c r="U6" t="n">
-        <v>680.1953629804475</v>
+        <v>810.6864484863765</v>
       </c>
       <c r="V6" t="n">
-        <v>398.6794199771851</v>
+        <v>801.0797139494875</v>
       </c>
       <c r="W6" t="n">
-        <v>371.029780674328</v>
+        <v>773.4300746466305</v>
       </c>
       <c r="X6" t="n">
-        <v>356.0169125476739</v>
+        <v>714.0686868686869</v>
       </c>
       <c r="Y6" t="n">
-        <v>356.0169125476739</v>
+        <v>714.0686868686869</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>266.2224381874042</v>
+        <v>986.8262762274139</v>
       </c>
       <c r="C7" t="n">
-        <v>266.2224381874042</v>
+        <v>1117.77828204585</v>
       </c>
       <c r="D7" t="n">
-        <v>384.4915823124043</v>
+        <v>1236.04742617085</v>
       </c>
       <c r="E7" t="n">
-        <v>507.2704865238173</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="F7" t="n">
-        <v>636.5814591157529</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="G7" t="n">
-        <v>795.1129791009988</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="H7" t="n">
-        <v>971.1350652440029</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="I7" t="n">
-        <v>1202.479291065332</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="J7" t="n">
-        <v>1215.536660124875</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="K7" t="n">
-        <v>1351.177579307644</v>
+        <v>1358.826330382263</v>
       </c>
       <c r="L7" t="n">
         <v>1358.826330382263</v>
@@ -4743,25 +4743,25 @@
         <v>27.2</v>
       </c>
       <c r="S7" t="n">
-        <v>72.44922788105838</v>
+        <v>27.2</v>
       </c>
       <c r="T7" t="n">
-        <v>266.2224381874042</v>
+        <v>220.9732103063458</v>
       </c>
       <c r="U7" t="n">
-        <v>266.2224381874042</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="V7" t="n">
-        <v>266.2224381874042</v>
+        <v>472.4839458954522</v>
       </c>
       <c r="W7" t="n">
-        <v>266.2224381874042</v>
+        <v>649.3248641551296</v>
       </c>
       <c r="X7" t="n">
-        <v>266.2224381874042</v>
+        <v>805.3056551793231</v>
       </c>
       <c r="Y7" t="n">
-        <v>266.2224381874042</v>
+        <v>921.6649558583554</v>
       </c>
     </row>
     <row r="8">
@@ -4801,19 +4801,19 @@
         <v>78.17329778894472</v>
       </c>
       <c r="L8" t="n">
-        <v>311.907366224194</v>
+        <v>431.6032977889447</v>
       </c>
       <c r="M8" t="n">
-        <v>665.3373662241941</v>
+        <v>785.0332977889448</v>
       </c>
       <c r="N8" t="n">
-        <v>1018.767366224194</v>
+        <v>1138.463297788945</v>
       </c>
       <c r="O8" t="n">
-        <v>1018.767366224194</v>
+        <v>1138.463297788945</v>
       </c>
       <c r="P8" t="n">
-        <v>1074.57</v>
+        <v>1194.265931564751</v>
       </c>
       <c r="Q8" t="n">
         <v>1428</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>574.0156713002057</v>
+        <v>678.7544038423301</v>
       </c>
       <c r="C9" t="n">
-        <v>574.0156713002057</v>
+        <v>362.026945318855</v>
       </c>
       <c r="D9" t="n">
-        <v>574.0156713002057</v>
+        <v>362.026945318855</v>
       </c>
       <c r="E9" t="n">
-        <v>574.0156713002057</v>
+        <v>362.026945318855</v>
       </c>
       <c r="F9" t="n">
-        <v>574.0156713002057</v>
+        <v>362.026945318855</v>
       </c>
       <c r="G9" t="n">
-        <v>574.0156713002057</v>
+        <v>362.026945318855</v>
       </c>
       <c r="H9" t="n">
-        <v>240.5487259813507</v>
+        <v>28.56</v>
       </c>
       <c r="I9" t="n">
         <v>28.56</v>
@@ -4877,19 +4877,19 @@
         <v>172.2326316847329</v>
       </c>
       <c r="K9" t="n">
-        <v>395.1234226847767</v>
+        <v>343.7536123162412</v>
       </c>
       <c r="L9" t="n">
-        <v>711.7849701290334</v>
+        <v>660.4151597604979</v>
       </c>
       <c r="M9" t="n">
-        <v>850.7414118718925</v>
+        <v>799.3716015033571</v>
       </c>
       <c r="N9" t="n">
-        <v>1038.29706421531</v>
+        <v>986.9272538467744</v>
       </c>
       <c r="O9" t="n">
-        <v>1326.990873823557</v>
+        <v>1275.621063455022</v>
       </c>
       <c r="P9" t="n">
         <v>1428</v>
@@ -4898,28 +4898,28 @@
         <v>1280.351723846095</v>
       </c>
       <c r="R9" t="n">
-        <v>919.7456632400339</v>
+        <v>1149.860638340165</v>
       </c>
       <c r="S9" t="n">
-        <v>626.2849132666058</v>
+        <v>1091.629706414791</v>
       </c>
       <c r="T9" t="n">
-        <v>626.2849132666058</v>
+        <v>1091.629706414791</v>
       </c>
       <c r="U9" t="n">
-        <v>626.2849132666058</v>
+        <v>1091.629706414791</v>
       </c>
       <c r="V9" t="n">
-        <v>616.6781787297168</v>
+        <v>1082.022971877902</v>
       </c>
       <c r="W9" t="n">
-        <v>589.0285394268598</v>
+        <v>1054.373332575045</v>
       </c>
       <c r="X9" t="n">
-        <v>574.0156713002057</v>
+        <v>1039.360464448391</v>
       </c>
       <c r="Y9" t="n">
-        <v>574.0156713002057</v>
+        <v>678.7544038423301</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145.2673376662921</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="C10" t="n">
-        <v>276.2193434847279</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="D10" t="n">
-        <v>394.488487609728</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="E10" t="n">
-        <v>517.267391821141</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="F10" t="n">
-        <v>646.5783644130765</v>
+        <v>409.3817081810419</v>
       </c>
       <c r="G10" t="n">
-        <v>805.1098843983225</v>
+        <v>567.9132281662878</v>
       </c>
       <c r="H10" t="n">
-        <v>981.1319705413266</v>
+        <v>743.9353143092919</v>
       </c>
       <c r="I10" t="n">
-        <v>1212.476196362655</v>
+        <v>975.2795401306207</v>
       </c>
       <c r="J10" t="n">
-        <v>1224.545411199493</v>
+        <v>1216.896660124875</v>
       </c>
       <c r="K10" t="n">
-        <v>1360.186330382263</v>
+        <v>1352.537579307645</v>
       </c>
       <c r="L10" t="n">
         <v>1360.186330382263</v>
@@ -4986,19 +4986,19 @@
         <v>28.56</v>
       </c>
       <c r="U10" t="n">
-        <v>28.56</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="V10" t="n">
-        <v>28.56</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="W10" t="n">
-        <v>28.56</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="X10" t="n">
-        <v>28.56</v>
+        <v>280.0707355891063</v>
       </c>
       <c r="Y10" t="n">
-        <v>28.56</v>
+        <v>280.0707355891063</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>168.830169545317</v>
+        <v>361.3221916367976</v>
       </c>
       <c r="C11" t="n">
-        <v>76.431605663505</v>
+        <v>268.9236277549856</v>
       </c>
       <c r="D11" t="n">
-        <v>76.431605663505</v>
+        <v>216.0557936743293</v>
       </c>
       <c r="E11" t="n">
-        <v>29.60000000000132</v>
+        <v>169.2241880108256</v>
       </c>
       <c r="F11" t="n">
-        <v>29.60000000000132</v>
+        <v>121.8609266896015</v>
       </c>
       <c r="G11" t="n">
-        <v>29.60000000000132</v>
+        <v>76.03930806559141</v>
       </c>
       <c r="H11" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I11" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J11" t="n">
-        <v>395.9000000000104</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="K11" t="n">
-        <v>445.5132977889551</v>
+        <v>79.21329778894577</v>
       </c>
       <c r="L11" t="n">
-        <v>507.0629808040305</v>
+        <v>325.2973662242239</v>
       </c>
       <c r="M11" t="n">
-        <v>873.3629808040396</v>
+        <v>691.5973662242316</v>
       </c>
       <c r="N11" t="n">
-        <v>1239.662980804049</v>
+        <v>1057.897366224239</v>
       </c>
       <c r="O11" t="n">
-        <v>1239.662980804049</v>
+        <v>1057.897366224239</v>
       </c>
       <c r="P11" t="n">
-        <v>1295.465614579854</v>
+        <v>1113.700000000045</v>
       </c>
       <c r="Q11" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="R11" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="S11" t="n">
-        <v>1350.837798118627</v>
+        <v>1350.837798118614</v>
       </c>
       <c r="T11" t="n">
-        <v>1121.594385276719</v>
+        <v>1350.837798118614</v>
       </c>
       <c r="U11" t="n">
-        <v>827.4632954174555</v>
+        <v>1161.293964444875</v>
       </c>
       <c r="V11" t="n">
-        <v>813.9358487343977</v>
+        <v>1161.293964444875</v>
       </c>
       <c r="W11" t="n">
-        <v>530.7303174405113</v>
+        <v>878.0884331509882</v>
       </c>
       <c r="X11" t="n">
-        <v>294.0820008135742</v>
+        <v>641.4401165240511</v>
       </c>
       <c r="Y11" t="n">
-        <v>294.0820008135742</v>
+        <v>486.5740229050547</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>578.1868959926508</v>
+        <v>578.1868959926505</v>
       </c>
       <c r="C12" t="n">
-        <v>575.055671300207</v>
+        <v>575.0556713002068</v>
       </c>
       <c r="D12" t="n">
-        <v>575.055671300207</v>
+        <v>575.0556713002068</v>
       </c>
       <c r="E12" t="n">
-        <v>575.055671300207</v>
+        <v>575.0556713002068</v>
       </c>
       <c r="F12" t="n">
-        <v>575.055671300207</v>
+        <v>575.0556713002068</v>
       </c>
       <c r="G12" t="n">
-        <v>575.055671300207</v>
+        <v>575.0556713002068</v>
       </c>
       <c r="H12" t="n">
-        <v>241.588725981352</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="I12" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J12" t="n">
-        <v>173.2726316847342</v>
+        <v>173.272631684734</v>
       </c>
       <c r="K12" t="n">
-        <v>396.163422684778</v>
+        <v>396.1634226847777</v>
       </c>
       <c r="L12" t="n">
-        <v>712.8249701290347</v>
+        <v>712.8249701290345</v>
       </c>
       <c r="M12" t="n">
-        <v>851.7814118718939</v>
+        <v>851.7814118718936</v>
       </c>
       <c r="N12" t="n">
-        <v>1038.92725384684</v>
+        <v>1039.337064215311</v>
       </c>
       <c r="O12" t="n">
-        <v>1327.621063455087</v>
+        <v>1327.621063455074</v>
       </c>
       <c r="P12" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="Q12" t="n">
-        <v>1332.35172384616</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="R12" t="n">
-        <v>1036.820973880587</v>
+        <v>1106.262626262663</v>
       </c>
       <c r="S12" t="n">
-        <v>931.1152944804645</v>
+        <v>1000.556946862541</v>
       </c>
       <c r="T12" t="n">
-        <v>884.1373917450303</v>
+        <v>953.579044127107</v>
       </c>
       <c r="U12" t="n">
-        <v>841.5146727191127</v>
+        <v>841.5146727191125</v>
       </c>
       <c r="V12" t="n">
-        <v>784.4331907074761</v>
+        <v>784.4331907074759</v>
       </c>
       <c r="W12" t="n">
-        <v>709.3088039298715</v>
+        <v>709.3088039298713</v>
       </c>
       <c r="X12" t="n">
-        <v>646.8211883284699</v>
+        <v>646.8211883284697</v>
       </c>
       <c r="Y12" t="n">
-        <v>605.01170068591</v>
+        <v>605.0117006859098</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>918.8336864105947</v>
+        <v>513.9407525180516</v>
       </c>
       <c r="C13" t="n">
-        <v>1003.255692229031</v>
+        <v>513.9407525180516</v>
       </c>
       <c r="D13" t="n">
-        <v>1074.994836354031</v>
+        <v>585.6798966430516</v>
       </c>
       <c r="E13" t="n">
-        <v>1151.243740565444</v>
+        <v>661.9288008544646</v>
       </c>
       <c r="F13" t="n">
-        <v>1234.024713157379</v>
+        <v>744.7097734464</v>
       </c>
       <c r="G13" t="n">
-        <v>1346.026233142625</v>
+        <v>744.7097734464</v>
       </c>
       <c r="H13" t="n">
-        <v>1475.518319285629</v>
+        <v>874.2018595894042</v>
       </c>
       <c r="I13" t="n">
-        <v>1480.000000000066</v>
+        <v>1059.016085410733</v>
       </c>
       <c r="J13" t="n">
-        <v>1480.000000000066</v>
+        <v>1390.889080817283</v>
       </c>
       <c r="K13" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="L13" t="n">
-        <v>1440.329304228836</v>
+        <v>1440.329304228824</v>
       </c>
       <c r="M13" t="n">
-        <v>1304.03663498632</v>
+        <v>1304.036634986307</v>
       </c>
       <c r="N13" t="n">
-        <v>1116.014518881456</v>
+        <v>1116.014518881443</v>
       </c>
       <c r="O13" t="n">
-        <v>855.9470340525121</v>
+        <v>855.9470340524989</v>
       </c>
       <c r="P13" t="n">
-        <v>544.7609148767392</v>
+        <v>750.5064258786513</v>
       </c>
       <c r="Q13" t="n">
-        <v>188.1535750529029</v>
+        <v>393.899086054815</v>
       </c>
       <c r="R13" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="S13" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="T13" t="n">
-        <v>176.8432103063471</v>
+        <v>176.8432103063469</v>
       </c>
       <c r="U13" t="n">
-        <v>381.8239458954534</v>
+        <v>381.8239458954532</v>
       </c>
       <c r="V13" t="n">
-        <v>539.0653387813994</v>
+        <v>381.8239458954532</v>
       </c>
       <c r="W13" t="n">
-        <v>669.3762570410768</v>
+        <v>443.7634148517594</v>
       </c>
       <c r="X13" t="n">
-        <v>778.8270480652703</v>
+        <v>443.7634148517594</v>
       </c>
       <c r="Y13" t="n">
-        <v>848.6563487443026</v>
+        <v>443.7634148517594</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>173.0470322524671</v>
+        <v>158.0364155611608</v>
       </c>
       <c r="C14" t="n">
-        <v>107.9211956433823</v>
+        <v>92.91057895207604</v>
       </c>
       <c r="D14" t="n">
-        <v>82.32608883545328</v>
+        <v>67.31547214414695</v>
       </c>
       <c r="E14" t="n">
-        <v>62.76721044467686</v>
+        <v>67.31547214414695</v>
       </c>
       <c r="F14" t="n">
-        <v>42.67667639618004</v>
+        <v>67.31547214414695</v>
       </c>
       <c r="G14" t="n">
-        <v>42.67667639618004</v>
+        <v>48.76658079286413</v>
       </c>
       <c r="H14" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I14" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J14" t="n">
-        <v>395.9000000000086</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="K14" t="n">
-        <v>762.2000000000248</v>
+        <v>79.21329778894577</v>
       </c>
       <c r="L14" t="n">
-        <v>1128.500000000041</v>
+        <v>325.2973662242246</v>
       </c>
       <c r="M14" t="n">
-        <v>1424.197366224253</v>
+        <v>691.597366224232</v>
       </c>
       <c r="N14" t="n">
-        <v>1424.197366224253</v>
+        <v>1057.897366224239</v>
       </c>
       <c r="O14" t="n">
-        <v>1424.197366224253</v>
+        <v>1057.897366224239</v>
       </c>
       <c r="P14" t="n">
-        <v>1480.000000000058</v>
+        <v>1113.700000000045</v>
       </c>
       <c r="Q14" t="n">
-        <v>1480.000000000058</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="R14" t="n">
-        <v>1480.000000000058</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="S14" t="n">
-        <v>1378.110525391347</v>
+        <v>1378.110525391341</v>
       </c>
       <c r="T14" t="n">
-        <v>1378.110525391347</v>
+        <v>1176.139839822161</v>
       </c>
       <c r="U14" t="n">
-        <v>1111.252162804811</v>
+        <v>909.2814772356245</v>
       </c>
       <c r="V14" t="n">
-        <v>863.9278959696351</v>
+        <v>661.9572104004488</v>
       </c>
       <c r="W14" t="n">
-        <v>607.9950919484759</v>
+        <v>592.9844752571695</v>
       </c>
       <c r="X14" t="n">
-        <v>398.619502594266</v>
+        <v>383.6088859029597</v>
       </c>
       <c r="Y14" t="n">
-        <v>271.0261362479969</v>
+        <v>256.0155195566906</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>372.6669114524022</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="C15" t="n">
-        <v>372.6669114524022</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="D15" t="n">
-        <v>372.6669114524022</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="E15" t="n">
-        <v>372.6669114524022</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="F15" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="G15" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="H15" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I15" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J15" t="n">
-        <v>173.2726316847342</v>
+        <v>173.272631684734</v>
       </c>
       <c r="K15" t="n">
-        <v>396.163422684778</v>
+        <v>396.1634226847777</v>
       </c>
       <c r="L15" t="n">
-        <v>712.8249701290347</v>
+        <v>712.8249701290345</v>
       </c>
       <c r="M15" t="n">
-        <v>851.7814118718939</v>
+        <v>851.7814118718936</v>
       </c>
       <c r="N15" t="n">
         <v>1039.337064215311</v>
       </c>
       <c r="O15" t="n">
-        <v>1327.62106345508</v>
+        <v>1327.621063455074</v>
       </c>
       <c r="P15" t="n">
-        <v>1480.000000000058</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="Q15" t="n">
-        <v>1480.000000000058</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="R15" t="n">
-        <v>1106.262626262668</v>
+        <v>1329.306894292103</v>
       </c>
       <c r="S15" t="n">
-        <v>1027.829674135273</v>
+        <v>955.569520554712</v>
       </c>
       <c r="T15" t="n">
-        <v>654.0923003978919</v>
+        <v>581.8321468173306</v>
       </c>
       <c r="U15" t="n">
-        <v>500.0789743946958</v>
+        <v>566.4821550641402</v>
       </c>
       <c r="V15" t="n">
-        <v>470.2702196557865</v>
+        <v>536.673400325231</v>
       </c>
       <c r="W15" t="n">
-        <v>422.4185601509092</v>
+        <v>162.9360265878497</v>
       </c>
       <c r="X15" t="n">
-        <v>387.2036718222349</v>
+        <v>44.13676036983373</v>
       </c>
       <c r="Y15" t="n">
-        <v>372.6669114524022</v>
+        <v>29.60000000000106</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>423.6588634165569</v>
+        <v>637.7897734464</v>
       </c>
       <c r="C16" t="n">
-        <v>534.8108692349927</v>
+        <v>637.7897734464</v>
       </c>
       <c r="D16" t="n">
-        <v>534.8108692349927</v>
+        <v>637.7897734464</v>
       </c>
       <c r="E16" t="n">
-        <v>637.7897734464057</v>
+        <v>637.7897734464</v>
       </c>
       <c r="F16" t="n">
-        <v>637.7897734464057</v>
+        <v>637.7897734464</v>
       </c>
       <c r="G16" t="n">
-        <v>637.7897734464057</v>
+        <v>637.7897734464</v>
       </c>
       <c r="H16" t="n">
-        <v>794.0118595894098</v>
+        <v>794.0118595894041</v>
       </c>
       <c r="I16" t="n">
-        <v>1005.556085410739</v>
+        <v>1005.556085410733</v>
       </c>
       <c r="J16" t="n">
-        <v>1364.159080817288</v>
+        <v>1364.159080817283</v>
       </c>
       <c r="K16" t="n">
-        <v>1480.000000000058</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="L16" t="n">
-        <v>1480.000000000058</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="M16" t="n">
-        <v>1370.98005803027</v>
+        <v>1370.980058030264</v>
       </c>
       <c r="N16" t="n">
-        <v>1210.230669198132</v>
+        <v>1210.230669198127</v>
       </c>
       <c r="O16" t="n">
-        <v>977.4359116419158</v>
+        <v>977.4359116419101</v>
       </c>
       <c r="P16" t="n">
-        <v>693.5225197388702</v>
+        <v>693.5225197388645</v>
       </c>
       <c r="Q16" t="n">
-        <v>364.1879071877611</v>
+        <v>364.1879071877554</v>
       </c>
       <c r="R16" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="S16" t="n">
-        <v>55.04922788105968</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="T16" t="n">
-        <v>229.0224381874055</v>
+        <v>64.03737059755082</v>
       </c>
       <c r="U16" t="n">
-        <v>229.0224381874055</v>
+        <v>64.03737059755082</v>
       </c>
       <c r="V16" t="n">
-        <v>229.0224381874055</v>
+        <v>248.0087634834968</v>
       </c>
       <c r="W16" t="n">
-        <v>386.0633564470829</v>
+        <v>405.0496817431742</v>
       </c>
       <c r="X16" t="n">
-        <v>423.6588634165569</v>
+        <v>541.2304727673677</v>
       </c>
       <c r="Y16" t="n">
-        <v>423.6588634165569</v>
+        <v>637.7897734464</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100.3692759762234</v>
+        <v>100.3692759762102</v>
       </c>
       <c r="C17" t="n">
-        <v>51.4050555287548</v>
+        <v>51.40505552874161</v>
       </c>
       <c r="D17" t="n">
-        <v>41.97156488244188</v>
+        <v>41.97156488242869</v>
       </c>
       <c r="E17" t="n">
-        <v>38.57430265328163</v>
+        <v>38.57430265326845</v>
       </c>
       <c r="F17" t="n">
-        <v>34.64538476640097</v>
+        <v>34.64538476638779</v>
       </c>
       <c r="G17" t="n">
-        <v>32.25810957673433</v>
+        <v>32.25810957672114</v>
       </c>
       <c r="H17" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I17" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J17" t="n">
-        <v>29.60000000000132</v>
+        <v>395.9000000000084</v>
       </c>
       <c r="K17" t="n">
-        <v>79.21329778894604</v>
+        <v>445.5132977889532</v>
       </c>
       <c r="L17" t="n">
-        <v>325.2973662242316</v>
+        <v>507.0629808040285</v>
       </c>
       <c r="M17" t="n">
-        <v>691.597366224239</v>
+        <v>691.597366224232</v>
       </c>
       <c r="N17" t="n">
-        <v>1057.897366224246</v>
+        <v>1057.897366224239</v>
       </c>
       <c r="O17" t="n">
-        <v>1057.897366224246</v>
+        <v>1057.897366224239</v>
       </c>
       <c r="P17" t="n">
-        <v>1113.700000000052</v>
+        <v>1113.700000000045</v>
       </c>
       <c r="Q17" t="n">
-        <v>1480.000000000059</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="R17" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="S17" t="n">
-        <v>1394.27214155297</v>
+        <v>1394.272141552957</v>
       </c>
       <c r="T17" t="n">
-        <v>1208.463072145406</v>
+        <v>1208.463072145393</v>
       </c>
       <c r="U17" t="n">
-        <v>957.7663257204862</v>
+        <v>957.766325720473</v>
       </c>
       <c r="V17" t="n">
-        <v>726.6036750469267</v>
+        <v>726.6036750469135</v>
       </c>
       <c r="W17" t="n">
-        <v>486.8324871873837</v>
+        <v>486.8324871873705</v>
       </c>
       <c r="X17" t="n">
-        <v>293.61851399479</v>
+        <v>293.6185139947768</v>
       </c>
       <c r="Y17" t="n">
-        <v>182.1867638101371</v>
+        <v>182.1867638101239</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>394.3473863086067</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="C18" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="D18" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="E18" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="F18" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="G18" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="H18" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I18" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J18" t="n">
-        <v>173.2726316847342</v>
+        <v>173.272631684734</v>
       </c>
       <c r="K18" t="n">
-        <v>396.163422684778</v>
+        <v>396.1634226847777</v>
       </c>
       <c r="L18" t="n">
-        <v>712.8249701290347</v>
+        <v>712.8249701290345</v>
       </c>
       <c r="M18" t="n">
-        <v>851.7814118718939</v>
+        <v>851.7814118718936</v>
       </c>
       <c r="N18" t="n">
         <v>1039.337064215311</v>
       </c>
       <c r="O18" t="n">
-        <v>1327.621063455081</v>
+        <v>1327.621063455074</v>
       </c>
       <c r="P18" t="n">
-        <v>1480.000000000059</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="Q18" t="n">
-        <v>1332.351723846154</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="R18" t="n">
-        <v>1197.820234299821</v>
+        <v>1345.46851045372</v>
       </c>
       <c r="S18" t="n">
-        <v>1135.548898334042</v>
+        <v>1283.197174487941</v>
       </c>
       <c r="T18" t="n">
-        <v>832.4752141336004</v>
+        <v>1279.65361518685</v>
       </c>
       <c r="U18" t="n">
-        <v>458.7378403962191</v>
+        <v>1279.65361518685</v>
       </c>
       <c r="V18" t="n">
-        <v>445.090701818926</v>
+        <v>1150.812121212145</v>
       </c>
       <c r="W18" t="n">
-        <v>413.4006584756648</v>
+        <v>777.0747474747637</v>
       </c>
       <c r="X18" t="n">
-        <v>394.3473863086067</v>
+        <v>403.3373737373824</v>
       </c>
       <c r="Y18" t="n">
-        <v>394.3473863086067</v>
+        <v>29.60000000000106</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1104.076348744303</v>
+        <v>254.7466383453254</v>
       </c>
       <c r="C19" t="n">
-        <v>1104.076348744303</v>
+        <v>337.6022314893725</v>
       </c>
       <c r="D19" t="n">
-        <v>1104.076348744303</v>
+        <v>451.9113756143726</v>
       </c>
       <c r="E19" t="n">
-        <v>1104.076348744303</v>
+        <v>570.7302798257856</v>
       </c>
       <c r="F19" t="n">
-        <v>1104.076348744303</v>
+        <v>696.0812524177211</v>
       </c>
       <c r="G19" t="n">
-        <v>1104.076348744303</v>
+        <v>850.652772402967</v>
       </c>
       <c r="H19" t="n">
-        <v>1104.076348744303</v>
+        <v>1022.714858545971</v>
       </c>
       <c r="I19" t="n">
-        <v>1104.076348744303</v>
+        <v>1250.0990843673</v>
       </c>
       <c r="J19" t="n">
-        <v>1385.468754624688</v>
+        <v>1250.0990843673</v>
       </c>
       <c r="K19" t="n">
-        <v>1385.468754624688</v>
+        <v>1381.78000355007</v>
       </c>
       <c r="L19" t="n">
         <v>1385.468754624688</v>
       </c>
       <c r="M19" t="n">
-        <v>1292.610428816516</v>
+        <v>1292.610428816515</v>
       </c>
       <c r="N19" t="n">
         <v>1148.022656145994</v>
       </c>
       <c r="O19" t="n">
-        <v>931.3895147513942</v>
+        <v>931.3895147513939</v>
       </c>
       <c r="P19" t="n">
-        <v>663.6377390099648</v>
+        <v>663.6377390099644</v>
       </c>
       <c r="Q19" t="n">
-        <v>350.4647426204718</v>
+        <v>350.4647426204716</v>
       </c>
       <c r="R19" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="S19" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="T19" t="n">
-        <v>219.4132103063471</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="U19" t="n">
-        <v>466.9639458954534</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="V19" t="n">
-        <v>666.7753387813993</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="W19" t="n">
-        <v>839.6562570410767</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="X19" t="n">
-        <v>991.6770480652702</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="Y19" t="n">
-        <v>1104.076348744303</v>
+        <v>141.9993006790333</v>
       </c>
     </row>
     <row r="20">
@@ -5719,52 +5719,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100.7161310307373</v>
+        <v>100.7161310307371</v>
       </c>
       <c r="C20" t="n">
-        <v>51.7519105832687</v>
+        <v>51.75191058326847</v>
       </c>
       <c r="D20" t="n">
-        <v>42.31841993695578</v>
+        <v>42.31841993695555</v>
       </c>
       <c r="E20" t="n">
-        <v>38.92115770779554</v>
+        <v>38.9211577077953</v>
       </c>
       <c r="F20" t="n">
-        <v>34.99223982091488</v>
+        <v>34.99223982091464</v>
       </c>
       <c r="G20" t="n">
-        <v>32.60496463124823</v>
+        <v>32.60496463124798</v>
       </c>
       <c r="H20" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I20" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J20" t="n">
-        <v>29.60000000000132</v>
+        <v>395.9000000000084</v>
       </c>
       <c r="K20" t="n">
-        <v>79.21329778894604</v>
+        <v>445.5132977889532</v>
       </c>
       <c r="L20" t="n">
-        <v>325.2973662242246</v>
+        <v>507.0629808040285</v>
       </c>
       <c r="M20" t="n">
-        <v>691.597366224232</v>
+        <v>873.3629808040359</v>
       </c>
       <c r="N20" t="n">
-        <v>1057.897366224239</v>
+        <v>1057.897366224232</v>
       </c>
       <c r="O20" t="n">
-        <v>1057.897366224239</v>
+        <v>1057.897366224232</v>
       </c>
       <c r="P20" t="n">
-        <v>1113.700000000045</v>
+        <v>1113.700000000038</v>
       </c>
       <c r="Q20" t="n">
-        <v>1480.000000000053</v>
+        <v>1480.000000000045</v>
       </c>
       <c r="R20" t="n">
         <v>1480.000000000053</v>
@@ -5776,19 +5776,19 @@
         <v>1208.80992719992</v>
       </c>
       <c r="U20" t="n">
-        <v>958.113180775</v>
+        <v>958.1131807749998</v>
       </c>
       <c r="V20" t="n">
-        <v>726.9505301014406</v>
+        <v>726.9505301014403</v>
       </c>
       <c r="W20" t="n">
-        <v>487.1793422418975</v>
+        <v>487.1793422418973</v>
       </c>
       <c r="X20" t="n">
-        <v>293.9653690493039</v>
+        <v>293.9653690493037</v>
       </c>
       <c r="Y20" t="n">
-        <v>182.5336188646509</v>
+        <v>182.5336188646507</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>930.7890689710384</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="C21" t="n">
-        <v>930.7890689710384</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="D21" t="n">
-        <v>930.7890689710384</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="E21" t="n">
-        <v>584.6556374337529</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="F21" t="n">
-        <v>241.588725981352</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="G21" t="n">
-        <v>241.588725981352</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="H21" t="n">
-        <v>241.588725981352</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="I21" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J21" t="n">
-        <v>173.2726316847342</v>
+        <v>173.272631684734</v>
       </c>
       <c r="K21" t="n">
-        <v>396.163422684778</v>
+        <v>396.1634226847777</v>
       </c>
       <c r="L21" t="n">
-        <v>712.8249701290347</v>
+        <v>712.8249701290345</v>
       </c>
       <c r="M21" t="n">
-        <v>851.7814118718939</v>
+        <v>851.7814118718936</v>
       </c>
       <c r="N21" t="n">
         <v>1039.337064215311</v>
       </c>
       <c r="O21" t="n">
-        <v>1327.621063455087</v>
+        <v>1327.621063455074</v>
       </c>
       <c r="P21" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="Q21" t="n">
-        <v>1480.000000000066</v>
+        <v>1332.351723846147</v>
       </c>
       <c r="R21" t="n">
-        <v>1345.468510453733</v>
+        <v>1197.820234299814</v>
       </c>
       <c r="S21" t="n">
-        <v>1283.197174487954</v>
+        <v>1135.548898334036</v>
       </c>
       <c r="T21" t="n">
-        <v>995.1795230586507</v>
+        <v>1020.753516799376</v>
       </c>
       <c r="U21" t="n">
-        <v>995.1795230586507</v>
+        <v>1020.753516799376</v>
       </c>
       <c r="V21" t="n">
-        <v>981.5323844813577</v>
+        <v>647.0161430619942</v>
       </c>
       <c r="W21" t="n">
-        <v>949.8423411380966</v>
+        <v>615.3260997187331</v>
       </c>
       <c r="X21" t="n">
-        <v>930.7890689710384</v>
+        <v>241.5887259813518</v>
       </c>
       <c r="Y21" t="n">
-        <v>930.7890689710384</v>
+        <v>241.5887259813518</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>125.8737514746109</v>
+        <v>533.6977278778961</v>
       </c>
       <c r="C22" t="n">
-        <v>125.8737514746109</v>
+        <v>660.6897336963319</v>
       </c>
       <c r="D22" t="n">
-        <v>240.182895599611</v>
+        <v>774.998877821332</v>
       </c>
       <c r="E22" t="n">
-        <v>359.001799811024</v>
+        <v>893.8177820327451</v>
       </c>
       <c r="F22" t="n">
-        <v>484.3527724029595</v>
+        <v>1019.168754624681</v>
       </c>
       <c r="G22" t="n">
-        <v>484.3527724029595</v>
+        <v>1019.168754624681</v>
       </c>
       <c r="H22" t="n">
-        <v>656.4148585459636</v>
+        <v>1019.168754624681</v>
       </c>
       <c r="I22" t="n">
-        <v>883.7990843672924</v>
+        <v>1019.168754624681</v>
       </c>
       <c r="J22" t="n">
-        <v>1250.0990843673</v>
+        <v>1385.468754624688</v>
       </c>
       <c r="K22" t="n">
-        <v>1381.78000355007</v>
+        <v>1385.468754624688</v>
       </c>
       <c r="L22" t="n">
         <v>1385.468754624688</v>
       </c>
       <c r="M22" t="n">
-        <v>1292.610428816516</v>
+        <v>1292.610428816515</v>
       </c>
       <c r="N22" t="n">
         <v>1148.022656145994</v>
       </c>
       <c r="O22" t="n">
-        <v>931.3895147513942</v>
+        <v>931.389514751394</v>
       </c>
       <c r="P22" t="n">
-        <v>663.6377390099648</v>
+        <v>663.6377390099645</v>
       </c>
       <c r="Q22" t="n">
-        <v>350.4647426204718</v>
+        <v>350.4647426204716</v>
       </c>
       <c r="R22" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="S22" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="T22" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="U22" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="V22" t="n">
-        <v>29.60000000000132</v>
+        <v>96.04868092773302</v>
       </c>
       <c r="W22" t="n">
-        <v>29.60000000000132</v>
+        <v>268.9295991874104</v>
       </c>
       <c r="X22" t="n">
-        <v>29.60000000000132</v>
+        <v>420.950390211604</v>
       </c>
       <c r="Y22" t="n">
-        <v>29.60000000000132</v>
+        <v>420.950390211604</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100.7161310307373</v>
+        <v>100.3692759762102</v>
       </c>
       <c r="C23" t="n">
-        <v>51.75191058326873</v>
+        <v>51.40505552874161</v>
       </c>
       <c r="D23" t="n">
-        <v>42.31841993695581</v>
+        <v>41.97156488242869</v>
       </c>
       <c r="E23" t="n">
-        <v>38.92115770779557</v>
+        <v>38.57430265326845</v>
       </c>
       <c r="F23" t="n">
-        <v>34.9922398209149</v>
+        <v>34.64538476638779</v>
       </c>
       <c r="G23" t="n">
-        <v>32.60496463124824</v>
+        <v>32.25810957672114</v>
       </c>
       <c r="H23" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I23" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J23" t="n">
-        <v>29.60000000000132</v>
+        <v>395.9000000000087</v>
       </c>
       <c r="K23" t="n">
-        <v>79.21329778894604</v>
+        <v>445.5132977889534</v>
       </c>
       <c r="L23" t="n">
-        <v>445.5132977889623</v>
+        <v>507.0629808040288</v>
       </c>
       <c r="M23" t="n">
-        <v>811.8132977889709</v>
+        <v>873.3629808040364</v>
       </c>
       <c r="N23" t="n">
-        <v>1057.897366224251</v>
+        <v>1239.662980804044</v>
       </c>
       <c r="O23" t="n">
-        <v>1057.897366224251</v>
+        <v>1239.662980804044</v>
       </c>
       <c r="P23" t="n">
-        <v>1113.700000000057</v>
+        <v>1295.46561457985</v>
       </c>
       <c r="Q23" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000046</v>
       </c>
       <c r="R23" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="S23" t="n">
-        <v>1394.618996607485</v>
+        <v>1394.272141552957</v>
       </c>
       <c r="T23" t="n">
-        <v>1208.80992719992</v>
+        <v>1208.463072145393</v>
       </c>
       <c r="U23" t="n">
-        <v>958.113180775</v>
+        <v>957.766325720473</v>
       </c>
       <c r="V23" t="n">
-        <v>726.9505301014406</v>
+        <v>726.6036750469135</v>
       </c>
       <c r="W23" t="n">
-        <v>487.1793422418975</v>
+        <v>486.8324871873705</v>
       </c>
       <c r="X23" t="n">
-        <v>293.9653690493039</v>
+        <v>293.6185139947768</v>
       </c>
       <c r="Y23" t="n">
-        <v>182.533618864651</v>
+        <v>182.1867638101239</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1070.252551977266</v>
+        <v>841.5257873618564</v>
       </c>
       <c r="C24" t="n">
-        <v>1070.252551977266</v>
+        <v>476.778401053251</v>
       </c>
       <c r="D24" t="n">
-        <v>718.8003429896878</v>
+        <v>476.778401053251</v>
       </c>
       <c r="E24" t="n">
-        <v>372.6669114524022</v>
+        <v>130.6449695159655</v>
       </c>
       <c r="F24" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="G24" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="H24" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="I24" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="J24" t="n">
-        <v>173.2726316847342</v>
+        <v>173.272631684734</v>
       </c>
       <c r="K24" t="n">
-        <v>396.163422684778</v>
+        <v>396.1634226847777</v>
       </c>
       <c r="L24" t="n">
-        <v>712.8249701290347</v>
+        <v>712.8249701290345</v>
       </c>
       <c r="M24" t="n">
-        <v>851.7814118718939</v>
+        <v>851.7814118718936</v>
       </c>
       <c r="N24" t="n">
         <v>1039.337064215311</v>
       </c>
       <c r="O24" t="n">
-        <v>1327.621063455087</v>
+        <v>1327.621063455074</v>
       </c>
       <c r="P24" t="n">
-        <v>1480.000000000066</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="Q24" t="n">
-        <v>1334.989390878081</v>
+        <v>1480.000000000053</v>
       </c>
       <c r="R24" t="n">
-        <v>1200.457901331748</v>
+        <v>1345.46851045372</v>
       </c>
       <c r="S24" t="n">
-        <v>1138.186565365969</v>
+        <v>1283.197174487941</v>
       </c>
       <c r="T24" t="n">
-        <v>1134.643006064879</v>
+        <v>1279.65361518685</v>
       </c>
       <c r="U24" t="n">
-        <v>1134.643006064879</v>
+        <v>1279.65361518685</v>
       </c>
       <c r="V24" t="n">
-        <v>1120.995867487585</v>
+        <v>1266.006476609557</v>
       </c>
       <c r="W24" t="n">
-        <v>1089.305824144324</v>
+        <v>1234.316433266296</v>
       </c>
       <c r="X24" t="n">
-        <v>1070.252551977266</v>
+        <v>1215.263161099238</v>
       </c>
       <c r="Y24" t="n">
-        <v>1070.252551977266</v>
+        <v>1215.263161099238</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1014.306872002904</v>
+        <v>437.9944514922655</v>
       </c>
       <c r="C25" t="n">
-        <v>1141.29887782134</v>
+        <v>564.9864573107012</v>
       </c>
       <c r="D25" t="n">
-        <v>1141.29887782134</v>
+        <v>679.2956014357013</v>
       </c>
       <c r="E25" t="n">
-        <v>1260.117782032753</v>
+        <v>798.1145056471144</v>
       </c>
       <c r="F25" t="n">
-        <v>1385.468754624688</v>
+        <v>923.4654782390498</v>
       </c>
       <c r="G25" t="n">
-        <v>1385.468754624688</v>
+        <v>1078.036998224296</v>
       </c>
       <c r="H25" t="n">
-        <v>1385.468754624688</v>
+        <v>1250.0990843673</v>
       </c>
       <c r="I25" t="n">
-        <v>1385.468754624688</v>
+        <v>1250.0990843673</v>
       </c>
       <c r="J25" t="n">
-        <v>1385.468754624688</v>
+        <v>1250.0990843673</v>
       </c>
       <c r="K25" t="n">
-        <v>1385.468754624688</v>
+        <v>1381.78000355007</v>
       </c>
       <c r="L25" t="n">
         <v>1385.468754624688</v>
       </c>
       <c r="M25" t="n">
-        <v>1292.610428816516</v>
+        <v>1292.610428816515</v>
       </c>
       <c r="N25" t="n">
-        <v>1148.022656145995</v>
+        <v>1148.022656145994</v>
       </c>
       <c r="O25" t="n">
-        <v>931.3895147513944</v>
+        <v>931.3895147513939</v>
       </c>
       <c r="P25" t="n">
-        <v>663.6377390099649</v>
+        <v>663.6377390099644</v>
       </c>
       <c r="Q25" t="n">
-        <v>350.4647426204719</v>
+        <v>350.4647426204716</v>
       </c>
       <c r="R25" t="n">
-        <v>29.60000000000132</v>
+        <v>29.60000000000106</v>
       </c>
       <c r="S25" t="n">
-        <v>29.60000000000132</v>
+        <v>70.88922788105941</v>
       </c>
       <c r="T25" t="n">
-        <v>29.60000000000132</v>
+        <v>70.88922788105941</v>
       </c>
       <c r="U25" t="n">
-        <v>277.1507355891076</v>
+        <v>70.88922788105941</v>
       </c>
       <c r="V25" t="n">
-        <v>476.9621284750536</v>
+        <v>70.88922788105941</v>
       </c>
       <c r="W25" t="n">
-        <v>649.8430467347309</v>
+        <v>212.8478131469411</v>
       </c>
       <c r="X25" t="n">
-        <v>801.8638377589244</v>
+        <v>212.8478131469411</v>
       </c>
       <c r="Y25" t="n">
-        <v>914.2631384379567</v>
+        <v>325.2471138259733</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>498.7668600782182</v>
+        <v>545.34380533602</v>
       </c>
       <c r="C26" t="n">
-        <v>498.7668600782182</v>
+        <v>406.4805949895614</v>
       </c>
       <c r="D26" t="n">
-        <v>399.4343795329154</v>
+        <v>307.1481144442586</v>
       </c>
       <c r="E26" t="n">
-        <v>306.1381274047652</v>
+        <v>213.8518623161085</v>
       </c>
       <c r="F26" t="n">
-        <v>212.3102196188947</v>
+        <v>120.0239545302379</v>
       </c>
       <c r="G26" t="n">
-        <v>120.0239545302381</v>
+        <v>120.0239545302379</v>
       </c>
       <c r="H26" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="I26" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="J26" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="K26" t="n">
-        <v>76.73329778894603</v>
+        <v>76.73329778894579</v>
       </c>
       <c r="L26" t="n">
-        <v>138.2829808040214</v>
+        <v>293.3673662242238</v>
       </c>
       <c r="M26" t="n">
-        <v>473.8929808040454</v>
+        <v>628.9773662242346</v>
       </c>
       <c r="N26" t="n">
-        <v>628.9773662242685</v>
+        <v>964.5873662242454</v>
       </c>
       <c r="O26" t="n">
-        <v>964.5873662242924</v>
+        <v>964.5873662242454</v>
       </c>
       <c r="P26" t="n">
-        <v>1020.390000000098</v>
+        <v>1020.390000000051</v>
       </c>
       <c r="Q26" t="n">
-        <v>1356.000000000122</v>
+        <v>1356.000000000062</v>
       </c>
       <c r="R26" t="n">
-        <v>1356.000000000122</v>
+        <v>1356.000000000062</v>
       </c>
       <c r="S26" t="n">
-        <v>1356.000000000122</v>
+        <v>1180.373151653977</v>
       </c>
       <c r="T26" t="n">
-        <v>1080.291940693568</v>
+        <v>904.6650923474226</v>
       </c>
       <c r="U26" t="n">
-        <v>1080.291940693568</v>
+        <v>866.4054459085694</v>
       </c>
       <c r="V26" t="n">
-        <v>759.2303001210187</v>
+        <v>545.34380533602</v>
       </c>
       <c r="W26" t="n">
-        <v>498.7668600782182</v>
+        <v>545.34380533602</v>
       </c>
       <c r="X26" t="n">
-        <v>498.7668600782182</v>
+        <v>545.34380533602</v>
       </c>
       <c r="Y26" t="n">
-        <v>498.7668600782182</v>
+        <v>545.34380533602</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>203.8947052433094</v>
+        <v>301.2182709496317</v>
       </c>
       <c r="C27" t="n">
-        <v>154.2988340862192</v>
+        <v>251.6223997925415</v>
       </c>
       <c r="D27" t="n">
-        <v>117.9981402501559</v>
+        <v>215.3217059564782</v>
       </c>
       <c r="E27" t="n">
-        <v>87.01622386438561</v>
+        <v>184.3397895707079</v>
       </c>
       <c r="F27" t="n">
-        <v>59.10082756349988</v>
+        <v>156.4243932698222</v>
       </c>
       <c r="G27" t="n">
-        <v>45.43543016734113</v>
+        <v>142.7589958736635</v>
       </c>
       <c r="H27" t="n">
-        <v>27.12000000000132</v>
+        <v>124.4435657063236</v>
       </c>
       <c r="I27" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="J27" t="n">
-        <v>48.8628213163195</v>
+        <v>170.792631684734</v>
       </c>
       <c r="K27" t="n">
-        <v>271.7536123163633</v>
+        <v>393.6834226847777</v>
       </c>
       <c r="L27" t="n">
-        <v>588.41515976062</v>
+        <v>710.3449701290344</v>
       </c>
       <c r="M27" t="n">
-        <v>727.3716015034792</v>
+        <v>849.3014118718936</v>
       </c>
       <c r="N27" t="n">
-        <v>914.9272538468965</v>
+        <v>1036.857064215311</v>
       </c>
       <c r="O27" t="n">
-        <v>1203.621063455144</v>
+        <v>1325.550873823558</v>
       </c>
       <c r="P27" t="n">
-        <v>1356.000000000122</v>
+        <v>1356.000000000062</v>
       </c>
       <c r="Q27" t="n">
-        <v>1258.67643429374</v>
+        <v>1356.000000000062</v>
       </c>
       <c r="R27" t="n">
-        <v>1034.245954848417</v>
+        <v>1131.569520554739</v>
       </c>
       <c r="S27" t="n">
-        <v>882.0756289836484</v>
+        <v>979.3991946899706</v>
       </c>
       <c r="T27" t="n">
-        <v>788.6330797835677</v>
+        <v>885.95664548989</v>
       </c>
       <c r="U27" t="n">
-        <v>699.5457142930036</v>
+        <v>796.8692799993258</v>
       </c>
       <c r="V27" t="n">
-        <v>595.9995858167206</v>
+        <v>693.3231515230428</v>
       </c>
       <c r="W27" t="n">
-        <v>474.4105525744695</v>
+        <v>571.7341182807918</v>
       </c>
       <c r="X27" t="n">
-        <v>365.4582905084215</v>
+        <v>462.7818562147438</v>
       </c>
       <c r="Y27" t="n">
-        <v>277.1841564012151</v>
+        <v>374.5077221075373</v>
       </c>
     </row>
     <row r="28">
@@ -6351,25 +6351,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>597.5736864105949</v>
+        <v>597.5736864105945</v>
       </c>
       <c r="C28" t="n">
-        <v>636.4556922290307</v>
+        <v>636.4556922290303</v>
       </c>
       <c r="D28" t="n">
-        <v>662.6548363540307</v>
+        <v>662.6548363540304</v>
       </c>
       <c r="E28" t="n">
-        <v>693.3637405654438</v>
+        <v>693.3637405654434</v>
       </c>
       <c r="F28" t="n">
-        <v>730.6047131573793</v>
+        <v>730.6047131573789</v>
       </c>
       <c r="G28" t="n">
-        <v>797.0662331426252</v>
+        <v>797.0662331426248</v>
       </c>
       <c r="H28" t="n">
-        <v>881.0183192856293</v>
+        <v>881.0183192856289</v>
       </c>
       <c r="I28" t="n">
         <v>1020.292545106958</v>
@@ -6384,43 +6384,43 @@
         <v>1264.061117460402</v>
       </c>
       <c r="M28" t="n">
-        <v>1081.30380175324</v>
+        <v>1264.061117460402</v>
       </c>
       <c r="N28" t="n">
-        <v>1081.30380175324</v>
+        <v>1264.061117460402</v>
       </c>
       <c r="O28" t="n">
-        <v>1081.30380175324</v>
+        <v>1102.164150718269</v>
       </c>
       <c r="P28" t="n">
-        <v>759.7399082940422</v>
+        <v>759.7399082940153</v>
       </c>
       <c r="Q28" t="n">
-        <v>417.3156658697754</v>
+        <v>417.3156658697618</v>
       </c>
       <c r="R28" t="n">
-        <v>74.89142344550855</v>
+        <v>74.89142344550829</v>
       </c>
       <c r="S28" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="T28" t="n">
-        <v>128.8232103063472</v>
+        <v>128.8232103063469</v>
       </c>
       <c r="U28" t="n">
-        <v>288.2639458954535</v>
+        <v>288.2639458954532</v>
       </c>
       <c r="V28" t="n">
-        <v>399.9653387813995</v>
+        <v>399.9653387813992</v>
       </c>
       <c r="W28" t="n">
-        <v>484.7362570410769</v>
+        <v>484.7362570410766</v>
       </c>
       <c r="X28" t="n">
-        <v>548.6470480652704</v>
+        <v>548.64704806527</v>
       </c>
       <c r="Y28" t="n">
-        <v>572.9363487443027</v>
+        <v>572.9363487443023</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>126.4524805453041</v>
+        <v>637.6300704246764</v>
       </c>
       <c r="C29" t="n">
-        <v>126.4524805453041</v>
+        <v>498.766860078218</v>
       </c>
       <c r="D29" t="n">
-        <v>27.12000000000132</v>
+        <v>399.4343795329152</v>
       </c>
       <c r="E29" t="n">
-        <v>27.12000000000132</v>
+        <v>306.138127404765</v>
       </c>
       <c r="F29" t="n">
-        <v>27.12000000000132</v>
+        <v>212.3102196188944</v>
       </c>
       <c r="G29" t="n">
-        <v>27.12000000000132</v>
+        <v>120.0239545302379</v>
       </c>
       <c r="H29" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="I29" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="J29" t="n">
-        <v>362.730000000015</v>
+        <v>362.7300000000101</v>
       </c>
       <c r="K29" t="n">
-        <v>567.4276832091572</v>
+        <v>412.3432977889549</v>
       </c>
       <c r="L29" t="n">
-        <v>628.9773662242326</v>
+        <v>473.8929808040302</v>
       </c>
       <c r="M29" t="n">
-        <v>964.5873662242462</v>
+        <v>809.5029808040393</v>
       </c>
       <c r="N29" t="n">
-        <v>1300.19736622426</v>
+        <v>964.5873662242436</v>
       </c>
       <c r="O29" t="n">
-        <v>1300.19736622426</v>
+        <v>964.5873662242436</v>
       </c>
       <c r="P29" t="n">
-        <v>1356.000000000066</v>
+        <v>1020.390000000049</v>
       </c>
       <c r="Q29" t="n">
-        <v>1356.000000000066</v>
+        <v>1356.000000000058</v>
       </c>
       <c r="R29" t="n">
-        <v>1356.000000000066</v>
+        <v>1356.000000000058</v>
       </c>
       <c r="S29" t="n">
-        <v>1356.000000000066</v>
+        <v>1356.000000000058</v>
       </c>
       <c r="T29" t="n">
-        <v>1356.000000000066</v>
+        <v>1356.000000000058</v>
       </c>
       <c r="U29" t="n">
-        <v>1356.000000000066</v>
+        <v>1015.404263676148</v>
       </c>
       <c r="V29" t="n">
-        <v>1034.938359427516</v>
+        <v>1015.404263676148</v>
       </c>
       <c r="W29" t="n">
-        <v>782.6126614534342</v>
+        <v>1010.677288241223</v>
       </c>
       <c r="X29" t="n">
-        <v>499.4996983618505</v>
+        <v>1010.677288241223</v>
       </c>
       <c r="Y29" t="n">
-        <v>298.1689582782077</v>
+        <v>809.3465481575799</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>301.2182709496353</v>
+        <v>203.8947052433091</v>
       </c>
       <c r="C30" t="n">
-        <v>251.6223997925451</v>
+        <v>154.2988340862189</v>
       </c>
       <c r="D30" t="n">
-        <v>117.9981402501559</v>
+        <v>117.9981402501557</v>
       </c>
       <c r="E30" t="n">
-        <v>87.01622386438561</v>
+        <v>87.01622386438532</v>
       </c>
       <c r="F30" t="n">
-        <v>59.10082756349988</v>
+        <v>59.10082756349961</v>
       </c>
       <c r="G30" t="n">
-        <v>45.43543016734113</v>
+        <v>45.43543016734087</v>
       </c>
       <c r="H30" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="I30" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="J30" t="n">
-        <v>170.7926316847342</v>
+        <v>170.792631684734</v>
       </c>
       <c r="K30" t="n">
-        <v>393.683422684778</v>
+        <v>393.6834226847777</v>
       </c>
       <c r="L30" t="n">
-        <v>710.3449701290347</v>
+        <v>710.3449701290344</v>
       </c>
       <c r="M30" t="n">
-        <v>849.3014118718938</v>
+        <v>849.3014118718936</v>
       </c>
       <c r="N30" t="n">
         <v>1036.857064215311</v>
       </c>
       <c r="O30" t="n">
-        <v>1325.550873823559</v>
+        <v>1325.550873823558</v>
       </c>
       <c r="P30" t="n">
-        <v>1356.000000000066</v>
+        <v>1356.000000000058</v>
       </c>
       <c r="Q30" t="n">
-        <v>1356.000000000066</v>
+        <v>1356.000000000058</v>
       </c>
       <c r="R30" t="n">
-        <v>1131.569520554743</v>
+        <v>1131.569520554735</v>
       </c>
       <c r="S30" t="n">
-        <v>979.3991946899743</v>
+        <v>979.399194689967</v>
       </c>
       <c r="T30" t="n">
-        <v>885.9566454898936</v>
+        <v>788.6330797835674</v>
       </c>
       <c r="U30" t="n">
-        <v>796.8692799993295</v>
+        <v>699.5457142930032</v>
       </c>
       <c r="V30" t="n">
-        <v>693.3231515230465</v>
+        <v>595.9995858167202</v>
       </c>
       <c r="W30" t="n">
-        <v>571.7341182807954</v>
+        <v>474.4105525744692</v>
       </c>
       <c r="X30" t="n">
-        <v>462.7818562147474</v>
+        <v>365.4582905084212</v>
       </c>
       <c r="Y30" t="n">
-        <v>374.507722107541</v>
+        <v>277.1841564012148</v>
       </c>
     </row>
     <row r="31">
@@ -6588,25 +6588,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>597.5736864105949</v>
+        <v>597.5736864105945</v>
       </c>
       <c r="C31" t="n">
-        <v>636.4556922290307</v>
+        <v>636.4556922290303</v>
       </c>
       <c r="D31" t="n">
-        <v>662.6548363540307</v>
+        <v>662.6548363540304</v>
       </c>
       <c r="E31" t="n">
-        <v>693.3637405654438</v>
+        <v>693.3637405654434</v>
       </c>
       <c r="F31" t="n">
-        <v>730.6047131573793</v>
+        <v>730.6047131573789</v>
       </c>
       <c r="G31" t="n">
-        <v>797.0662331426252</v>
+        <v>797.0662331426248</v>
       </c>
       <c r="H31" t="n">
-        <v>881.0183192856293</v>
+        <v>881.0183192856289</v>
       </c>
       <c r="I31" t="n">
         <v>1020.292545106958</v>
@@ -6618,46 +6618,46 @@
         <v>1350.196459696278</v>
       </c>
       <c r="L31" t="n">
-        <v>1264.061117460402</v>
+        <v>1350.196459696278</v>
       </c>
       <c r="M31" t="n">
-        <v>1264.061117460402</v>
+        <v>1350.196459696278</v>
       </c>
       <c r="N31" t="n">
-        <v>1029.574354890891</v>
+        <v>1350.196459696278</v>
       </c>
       <c r="O31" t="n">
-        <v>723.0422235973008</v>
+        <v>1043.664328402687</v>
       </c>
       <c r="P31" t="n">
-        <v>380.6179811730444</v>
+        <v>711.9684848485044</v>
       </c>
       <c r="Q31" t="n">
-        <v>38.19373874878795</v>
+        <v>369.5442424242527</v>
       </c>
       <c r="R31" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="S31" t="n">
-        <v>27.12000000000132</v>
+        <v>27.12000000000106</v>
       </c>
       <c r="T31" t="n">
-        <v>128.8232103063472</v>
+        <v>128.8232103063469</v>
       </c>
       <c r="U31" t="n">
-        <v>288.2639458954535</v>
+        <v>288.2639458954532</v>
       </c>
       <c r="V31" t="n">
-        <v>399.9653387813995</v>
+        <v>399.9653387813992</v>
       </c>
       <c r="W31" t="n">
-        <v>484.7362570410769</v>
+        <v>484.7362570410766</v>
       </c>
       <c r="X31" t="n">
-        <v>548.6470480652704</v>
+        <v>548.64704806527</v>
       </c>
       <c r="Y31" t="n">
-        <v>572.9363487443027</v>
+        <v>572.9363487443023</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>56.54240226565174</v>
+        <v>56.54240226565148</v>
       </c>
       <c r="C32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="D32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="E32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="F32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="G32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="H32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="I32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="J32" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="K32" t="n">
-        <v>75.37329778894603</v>
+        <v>75.37329778894578</v>
       </c>
       <c r="L32" t="n">
-        <v>275.8573662242109</v>
+        <v>136.9229808040212</v>
       </c>
       <c r="M32" t="n">
-        <v>594.6373662242272</v>
+        <v>455.7029808040342</v>
       </c>
       <c r="N32" t="n">
-        <v>913.4173662242436</v>
+        <v>774.4829808040472</v>
       </c>
       <c r="O32" t="n">
-        <v>913.4173662242436</v>
+        <v>1093.26298080406</v>
       </c>
       <c r="P32" t="n">
-        <v>969.2200000000494</v>
+        <v>1149.065614579866</v>
       </c>
       <c r="Q32" t="n">
-        <v>1288.000000000066</v>
+        <v>1288.000000000053</v>
       </c>
       <c r="R32" t="n">
-        <v>1288.000000000066</v>
+        <v>1288.000000000053</v>
       </c>
       <c r="S32" t="n">
-        <v>1220.453959734788</v>
+        <v>1220.453959734775</v>
       </c>
       <c r="T32" t="n">
-        <v>1052.826708509042</v>
+        <v>1055.545289343925</v>
       </c>
       <c r="U32" t="n">
-        <v>820.3117802659405</v>
+        <v>823.0303611008233</v>
       </c>
       <c r="V32" t="n">
-        <v>607.3309477741991</v>
+        <v>610.0495286090819</v>
       </c>
       <c r="W32" t="n">
-        <v>385.7415780964743</v>
+        <v>388.4601589313571</v>
       </c>
       <c r="X32" t="n">
-        <v>210.7094230856988</v>
+        <v>213.4280039205817</v>
       </c>
       <c r="Y32" t="n">
-        <v>117.4594910828641</v>
+        <v>120.1780719177469</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="C33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="D33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="E33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="F33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="G33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="H33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="I33" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="J33" t="n">
-        <v>169.4326316847342</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="K33" t="n">
-        <v>392.3234226847781</v>
+        <v>203.7536123162939</v>
       </c>
       <c r="L33" t="n">
-        <v>672.794096305542</v>
+        <v>520.4151597605506</v>
       </c>
       <c r="M33" t="n">
-        <v>811.7505380484012</v>
+        <v>659.3716015034098</v>
       </c>
       <c r="N33" t="n">
-        <v>999.3061903918185</v>
+        <v>846.9272538468272</v>
       </c>
       <c r="O33" t="n">
-        <v>1288.000000000066</v>
+        <v>1135.621063455074</v>
       </c>
       <c r="P33" t="n">
-        <v>1288.000000000066</v>
+        <v>1288.000000000053</v>
       </c>
       <c r="Q33" t="n">
-        <v>1140.35172384616</v>
+        <v>1140.351723846147</v>
       </c>
       <c r="R33" t="n">
-        <v>815.0991985936183</v>
+        <v>1015.02580091906</v>
       </c>
       <c r="S33" t="n">
-        <v>577.3809303805768</v>
+        <v>689.7732756665212</v>
       </c>
       <c r="T33" t="n">
-        <v>252.1284051280349</v>
+        <v>364.5207504139826</v>
       </c>
       <c r="U33" t="n">
-        <v>252.1284051280349</v>
+        <v>364.5207504139826</v>
       </c>
       <c r="V33" t="n">
-        <v>252.1284051280349</v>
+        <v>364.5207504139826</v>
       </c>
       <c r="W33" t="n">
-        <v>238.620179966592</v>
+        <v>351.0125252525397</v>
       </c>
       <c r="X33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="Y33" t="n">
-        <v>237.748725981352</v>
+        <v>25.76000000000106</v>
       </c>
     </row>
     <row r="34">
@@ -6825,31 +6825,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>456.3874293695193</v>
+        <v>357.4114391153989</v>
       </c>
       <c r="C34" t="n">
-        <v>601.199435187955</v>
+        <v>357.4114391153989</v>
       </c>
       <c r="D34" t="n">
-        <v>733.3285793129551</v>
+        <v>357.4114391153989</v>
       </c>
       <c r="E34" t="n">
-        <v>869.9674835243682</v>
+        <v>494.050343326812</v>
       </c>
       <c r="F34" t="n">
-        <v>1013.138456116304</v>
+        <v>494.050343326812</v>
       </c>
       <c r="G34" t="n">
-        <v>1013.138456116304</v>
+        <v>666.4418633120579</v>
       </c>
       <c r="H34" t="n">
-        <v>1203.020542259308</v>
+        <v>856.323949455062</v>
       </c>
       <c r="I34" t="n">
-        <v>1251.029094459161</v>
+        <v>1101.528175276391</v>
       </c>
       <c r="J34" t="n">
-        <v>1251.029094459161</v>
+        <v>1101.528175276391</v>
       </c>
       <c r="K34" t="n">
         <v>1251.029094459161</v>
@@ -6864,37 +6864,37 @@
         <v>1071.455383418722</v>
       </c>
       <c r="O34" t="n">
-        <v>873.0040602059397</v>
+        <v>873.0040602059395</v>
       </c>
       <c r="P34" t="n">
-        <v>623.4341026463284</v>
+        <v>623.4341026463281</v>
       </c>
       <c r="Q34" t="n">
-        <v>328.4429244386536</v>
+        <v>328.4429244386534</v>
       </c>
       <c r="R34" t="n">
-        <v>25.76000000000132</v>
+        <v>25.76000000000106</v>
       </c>
       <c r="S34" t="n">
-        <v>25.76000000000132</v>
+        <v>84.86922788105942</v>
       </c>
       <c r="T34" t="n">
-        <v>25.76000000000132</v>
+        <v>227.1921384363667</v>
       </c>
       <c r="U34" t="n">
-        <v>25.76000000000132</v>
+        <v>227.1921384363667</v>
       </c>
       <c r="V34" t="n">
-        <v>25.76000000000132</v>
+        <v>227.1921384363667</v>
       </c>
       <c r="W34" t="n">
-        <v>25.76000000000132</v>
+        <v>227.1921384363667</v>
       </c>
       <c r="X34" t="n">
-        <v>195.6007910241948</v>
+        <v>227.1921384363667</v>
       </c>
       <c r="Y34" t="n">
-        <v>325.8200917032271</v>
+        <v>357.4114391153989</v>
       </c>
     </row>
     <row r="35">
@@ -6904,40 +6904,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>50.30866991555158</v>
+        <v>49.44179620504435</v>
       </c>
       <c r="C35" t="n">
-        <v>25.58687371050722</v>
+        <v>24.72</v>
       </c>
       <c r="D35" t="n">
-        <v>25.58687371050722</v>
+        <v>24.72</v>
       </c>
       <c r="E35" t="n">
-        <v>25.58687371050722</v>
+        <v>24.72</v>
       </c>
       <c r="F35" t="n">
-        <v>25.58687371050722</v>
+        <v>24.72</v>
       </c>
       <c r="G35" t="n">
-        <v>25.58687371050722</v>
+        <v>24.72</v>
       </c>
       <c r="H35" t="n">
-        <v>25.58687371050722</v>
+        <v>24.72</v>
       </c>
       <c r="I35" t="n">
         <v>24.72</v>
       </c>
       <c r="J35" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="K35" t="n">
         <v>330.63</v>
       </c>
-      <c r="K35" t="n">
-        <v>380.2432977889447</v>
-      </c>
       <c r="L35" t="n">
-        <v>441.7929808040201</v>
+        <v>392.1796830150754</v>
       </c>
       <c r="M35" t="n">
-        <v>568.377366224194</v>
+        <v>698.0896830150755</v>
       </c>
       <c r="N35" t="n">
         <v>874.2873662241941</v>
@@ -6952,28 +6952,28 @@
         <v>1236</v>
       </c>
       <c r="R35" t="n">
-        <v>1236</v>
+        <v>1235.133126289493</v>
       </c>
       <c r="S35" t="n">
-        <v>1174.514565795329</v>
+        <v>1173.647692084822</v>
       </c>
       <c r="T35" t="n">
-        <v>1012.947920630189</v>
+        <v>1012.081046919682</v>
       </c>
       <c r="U35" t="n">
-        <v>786.4935984476931</v>
+        <v>785.6267247371859</v>
       </c>
       <c r="V35" t="n">
-        <v>579.5733720165579</v>
+        <v>578.7064983060507</v>
       </c>
       <c r="W35" t="n">
-        <v>364.0446083994391</v>
+        <v>363.1777346889319</v>
       </c>
       <c r="X35" t="n">
-        <v>195.0730594492697</v>
+        <v>194.2061857387624</v>
       </c>
       <c r="Y35" t="n">
-        <v>107.883733507041</v>
+        <v>107.0168597965338</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>932.5861277179944</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="C36" t="n">
-        <v>620.4649155967822</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="D36" t="n">
-        <v>620.4649155967822</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="E36" t="n">
-        <v>620.4649155967822</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="F36" t="n">
-        <v>308.3437034755701</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="G36" t="n">
-        <v>308.3437034755701</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="H36" t="n">
         <v>236.7087259813507</v>
@@ -7007,10 +7007,10 @@
         <v>24.72</v>
       </c>
       <c r="J36" t="n">
-        <v>168.3926316847329</v>
+        <v>91.99330530543247</v>
       </c>
       <c r="K36" t="n">
-        <v>391.2834226847767</v>
+        <v>314.8840963054762</v>
       </c>
       <c r="L36" t="n">
         <v>620.7940963054763</v>
@@ -7031,28 +7031,28 @@
         <v>1088.351723846095</v>
       </c>
       <c r="R36" t="n">
-        <v>978.0626585421855</v>
+        <v>898.9800619471293</v>
       </c>
       <c r="S36" t="n">
-        <v>940.0337468188312</v>
+        <v>860.951150223775</v>
       </c>
       <c r="T36" t="n">
-        <v>940.0337468188312</v>
+        <v>860.951150223775</v>
       </c>
       <c r="U36" t="n">
-        <v>940.0337468188312</v>
+        <v>860.951150223775</v>
       </c>
       <c r="V36" t="n">
-        <v>940.0337468188312</v>
+        <v>860.951150223775</v>
       </c>
       <c r="W36" t="n">
-        <v>932.5861277179944</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="X36" t="n">
-        <v>932.5861277179944</v>
+        <v>548.8299381025629</v>
       </c>
       <c r="Y36" t="n">
-        <v>932.5861277179944</v>
+        <v>548.8299381025629</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>432.5380732553984</v>
+        <v>771.59649057634</v>
       </c>
       <c r="C37" t="n">
-        <v>583.2900790738341</v>
+        <v>771.59649057634</v>
       </c>
       <c r="D37" t="n">
-        <v>721.3592231988342</v>
+        <v>909.6656347013401</v>
       </c>
       <c r="E37" t="n">
-        <v>721.3592231988342</v>
+        <v>1052.244538912753</v>
       </c>
       <c r="F37" t="n">
-        <v>870.4701957907697</v>
+        <v>1052.244538912753</v>
       </c>
       <c r="G37" t="n">
-        <v>870.4701957907697</v>
+        <v>1052.244538912753</v>
       </c>
       <c r="H37" t="n">
-        <v>1066.292281933774</v>
+        <v>1052.244538912753</v>
       </c>
       <c r="I37" t="n">
-        <v>1235.134209170142</v>
+        <v>1052.244538912753</v>
       </c>
       <c r="J37" t="n">
-        <v>1235.134209170142</v>
+        <v>1052.244538912753</v>
       </c>
       <c r="K37" t="n">
-        <v>1235.134209170142</v>
+        <v>1207.685458095523</v>
       </c>
       <c r="L37" t="n">
         <v>1235.134209170142</v>
@@ -7101,37 +7101,37 @@
         <v>1046.172959176296</v>
       </c>
       <c r="O37" t="n">
-        <v>853.7822420241201</v>
+        <v>853.7822420241203</v>
       </c>
       <c r="P37" t="n">
-        <v>610.2728905251149</v>
+        <v>610.272890525115</v>
       </c>
       <c r="Q37" t="n">
-        <v>321.3423183780462</v>
+        <v>321.3423183780463</v>
       </c>
       <c r="R37" t="n">
         <v>24.72</v>
       </c>
       <c r="S37" t="n">
-        <v>24.72</v>
+        <v>89.76922788105837</v>
       </c>
       <c r="T37" t="n">
-        <v>24.72</v>
+        <v>89.76922788105837</v>
       </c>
       <c r="U37" t="n">
-        <v>296.0307355891063</v>
+        <v>302.2889339713382</v>
       </c>
       <c r="V37" t="n">
-        <v>296.0307355891063</v>
+        <v>302.2889339713382</v>
       </c>
       <c r="W37" t="n">
-        <v>296.0307355891063</v>
+        <v>498.9298522310156</v>
       </c>
       <c r="X37" t="n">
-        <v>296.0307355891063</v>
+        <v>498.9298522310156</v>
       </c>
       <c r="Y37" t="n">
-        <v>296.0307355891063</v>
+        <v>635.0891529100479</v>
       </c>
     </row>
     <row r="38">
@@ -7165,13 +7165,13 @@
         <v>24.72</v>
       </c>
       <c r="J38" t="n">
-        <v>24.72</v>
+        <v>330.63</v>
       </c>
       <c r="K38" t="n">
-        <v>330.63</v>
+        <v>380.2432977889447</v>
       </c>
       <c r="L38" t="n">
-        <v>392.1796830150754</v>
+        <v>441.7929808040201</v>
       </c>
       <c r="M38" t="n">
         <v>568.377366224194</v>
@@ -7189,13 +7189,13 @@
         <v>1236</v>
       </c>
       <c r="R38" t="n">
-        <v>1235.133126289493</v>
+        <v>1236</v>
       </c>
       <c r="S38" t="n">
-        <v>1173.647692084822</v>
+        <v>1174.514565795329</v>
       </c>
       <c r="T38" t="n">
-        <v>1012.081046919682</v>
+        <v>1012.947920630189</v>
       </c>
       <c r="U38" t="n">
         <v>785.6267247371859</v>
@@ -7220,46 +7220,46 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>932.5861277179944</v>
+        <v>456.6616805028333</v>
       </c>
       <c r="C39" t="n">
-        <v>620.4649155967822</v>
+        <v>456.6616805028333</v>
       </c>
       <c r="D39" t="n">
-        <v>336.8412121212122</v>
+        <v>144.5404683816212</v>
       </c>
       <c r="E39" t="n">
-        <v>336.8412121212122</v>
+        <v>144.5404683816212</v>
       </c>
       <c r="F39" t="n">
-        <v>24.72</v>
+        <v>144.5404683816212</v>
       </c>
       <c r="G39" t="n">
-        <v>24.72</v>
+        <v>144.5404683816212</v>
       </c>
       <c r="H39" t="n">
-        <v>24.72</v>
+        <v>144.5404683816212</v>
       </c>
       <c r="I39" t="n">
         <v>24.72</v>
       </c>
       <c r="J39" t="n">
-        <v>168.3926316847329</v>
+        <v>24.72</v>
       </c>
       <c r="K39" t="n">
-        <v>391.2834226847767</v>
+        <v>247.6107910000438</v>
       </c>
       <c r="L39" t="n">
-        <v>697.1934226847768</v>
+        <v>553.5207910000438</v>
       </c>
       <c r="M39" t="n">
-        <v>759.7505380483354</v>
+        <v>607.3716015033571</v>
       </c>
       <c r="N39" t="n">
-        <v>947.3061903917528</v>
+        <v>794.9272538467744</v>
       </c>
       <c r="O39" t="n">
-        <v>1236</v>
+        <v>1083.621063455022</v>
       </c>
       <c r="P39" t="n">
         <v>1236</v>
@@ -7268,28 +7268,28 @@
         <v>1088.351723846095</v>
       </c>
       <c r="R39" t="n">
-        <v>978.0626585421855</v>
+        <v>776.2305117248824</v>
       </c>
       <c r="S39" t="n">
-        <v>940.0337468188312</v>
+        <v>464.1092996036703</v>
       </c>
       <c r="T39" t="n">
-        <v>940.0337468188312</v>
+        <v>464.1092996036703</v>
       </c>
       <c r="U39" t="n">
-        <v>940.0337468188312</v>
+        <v>464.1092996036703</v>
       </c>
       <c r="V39" t="n">
-        <v>940.0337468188312</v>
+        <v>464.1092996036703</v>
       </c>
       <c r="W39" t="n">
-        <v>932.5861277179944</v>
+        <v>456.6616805028333</v>
       </c>
       <c r="X39" t="n">
-        <v>932.5861277179944</v>
+        <v>456.6616805028333</v>
       </c>
       <c r="Y39" t="n">
-        <v>932.5861277179944</v>
+        <v>456.6616805028333</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="C40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="D40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="E40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="F40" t="n">
-        <v>574.6531737765105</v>
+        <v>121.0367069631742</v>
       </c>
       <c r="G40" t="n">
-        <v>605.2782269484203</v>
+        <v>299.3682269484201</v>
       </c>
       <c r="H40" t="n">
-        <v>801.1003130914244</v>
+        <v>495.1903130914242</v>
       </c>
       <c r="I40" t="n">
-        <v>1052.244538912753</v>
+        <v>746.334538912753</v>
       </c>
       <c r="J40" t="n">
         <v>1052.244538912753</v>
@@ -7350,25 +7350,25 @@
         <v>24.72</v>
       </c>
       <c r="S40" t="n">
-        <v>89.76922788105836</v>
+        <v>24.72</v>
       </c>
       <c r="T40" t="n">
-        <v>303.3424381874042</v>
+        <v>24.72</v>
       </c>
       <c r="U40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="V40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="W40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="X40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
       <c r="Y40" t="n">
-        <v>574.6531737765105</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="41">
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>491.3163550277118</v>
+        <v>299.6363636361788</v>
       </c>
       <c r="C41" t="n">
-        <v>491.3163550277118</v>
+        <v>299.6363636361788</v>
       </c>
       <c r="D41" t="n">
-        <v>392.99397549251</v>
+        <v>299.6363636361788</v>
       </c>
       <c r="E41" t="n">
-        <v>300.7078243744609</v>
+        <v>299.6363636361788</v>
       </c>
       <c r="F41" t="n">
         <v>207.8900175986913</v>
@@ -7435,19 +7435,19 @@
         <v>1236</v>
       </c>
       <c r="U41" t="n">
-        <v>1236</v>
+        <v>923.8787878787239</v>
       </c>
       <c r="V41" t="n">
-        <v>923.8787878787273</v>
+        <v>611.7575757574514</v>
       </c>
       <c r="W41" t="n">
-        <v>862.3433708240561</v>
+        <v>299.6363636361788</v>
       </c>
       <c r="X41" t="n">
-        <v>862.3433708240561</v>
+        <v>299.6363636361788</v>
       </c>
       <c r="Y41" t="n">
-        <v>662.0227317505144</v>
+        <v>299.6363636361788</v>
       </c>
     </row>
     <row r="42">
@@ -7481,16 +7481,16 @@
         <v>24.72</v>
       </c>
       <c r="J42" t="n">
-        <v>24.72</v>
+        <v>168.3926316847329</v>
       </c>
       <c r="K42" t="n">
-        <v>247.6107910000438</v>
+        <v>391.2834226847767</v>
       </c>
       <c r="L42" t="n">
-        <v>553.5207910000438</v>
+        <v>655.9708121039153</v>
       </c>
       <c r="M42" t="n">
-        <v>692.477232742903</v>
+        <v>794.9272538467744</v>
       </c>
       <c r="N42" t="n">
         <v>794.9272538467744</v>
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>602.1036864105935</v>
+        <v>474.4672267143171</v>
       </c>
       <c r="C43" t="n">
-        <v>641.9756922290293</v>
+        <v>514.3392325327528</v>
       </c>
       <c r="D43" t="n">
-        <v>669.1648363540294</v>
+        <v>541.5283766577529</v>
       </c>
       <c r="E43" t="n">
-        <v>700.8637405654424</v>
+        <v>573.227280869166</v>
       </c>
       <c r="F43" t="n">
-        <v>739.0947131573779</v>
+        <v>611.4582534611014</v>
       </c>
       <c r="G43" t="n">
-        <v>806.5462331426238</v>
+        <v>678.9097734463473</v>
       </c>
       <c r="H43" t="n">
-        <v>891.488319285628</v>
+        <v>763.8518595893515</v>
       </c>
       <c r="I43" t="n">
-        <v>1031.752545106957</v>
+        <v>904.1160854106803</v>
       </c>
       <c r="J43" t="n">
         <v>1191.43908081723</v>
@@ -7566,46 +7566,46 @@
         <v>1236</v>
       </c>
       <c r="L43" t="n">
-        <v>1150.874758774225</v>
+        <v>1236</v>
       </c>
       <c r="M43" t="n">
-        <v>969.127544077164</v>
+        <v>1236</v>
       </c>
       <c r="N43" t="n">
-        <v>735.6508825177539</v>
+        <v>1002.52333844059</v>
       </c>
       <c r="O43" t="n">
-        <v>430.1288522342646</v>
+        <v>697.0013081571007</v>
       </c>
       <c r="P43" t="n">
-        <v>118.0076401129358</v>
+        <v>384.880096035761</v>
       </c>
       <c r="Q43" t="n">
-        <v>71.48132243540623</v>
+        <v>72.75888391442163</v>
       </c>
       <c r="R43" t="n">
-        <v>71.48132243540623</v>
+        <v>24.72</v>
       </c>
       <c r="S43" t="n">
         <v>24.72</v>
       </c>
       <c r="T43" t="n">
-        <v>127.4132103063458</v>
+        <v>24.72</v>
       </c>
       <c r="U43" t="n">
-        <v>287.8439458954522</v>
+        <v>160.2074861991758</v>
       </c>
       <c r="V43" t="n">
-        <v>400.5353387813981</v>
+        <v>272.8988790851217</v>
       </c>
       <c r="W43" t="n">
-        <v>486.2962570410755</v>
+        <v>358.6597973447991</v>
       </c>
       <c r="X43" t="n">
-        <v>551.1970480652691</v>
+        <v>423.5605883689927</v>
       </c>
       <c r="Y43" t="n">
-        <v>576.4763487443014</v>
+        <v>448.8398890480249</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>627.6799913913483</v>
+        <v>24.72</v>
       </c>
       <c r="C44" t="n">
-        <v>627.6799913913483</v>
+        <v>24.72</v>
       </c>
       <c r="D44" t="n">
-        <v>502.0848845834191</v>
+        <v>24.72</v>
       </c>
       <c r="E44" t="n">
-        <v>382.5260061926427</v>
+        <v>24.72</v>
       </c>
       <c r="F44" t="n">
-        <v>262.4354721441459</v>
+        <v>24.72</v>
       </c>
       <c r="G44" t="n">
-        <v>143.8865807928631</v>
+        <v>24.72</v>
       </c>
       <c r="H44" t="n">
         <v>24.72</v>
@@ -7645,13 +7645,13 @@
         <v>74.33329778894472</v>
       </c>
       <c r="L44" t="n">
-        <v>262.467366224194</v>
+        <v>135.8829808040201</v>
       </c>
       <c r="M44" t="n">
+        <v>441.7929808040201</v>
+      </c>
+      <c r="N44" t="n">
         <v>568.377366224194</v>
-      </c>
-      <c r="N44" t="n">
-        <v>874.2873662241941</v>
       </c>
       <c r="O44" t="n">
         <v>874.2873662241941</v>
@@ -7669,22 +7669,22 @@
         <v>1236</v>
       </c>
       <c r="T44" t="n">
-        <v>934.0293144308196</v>
+        <v>1236</v>
       </c>
       <c r="U44" t="n">
-        <v>627.6799913913483</v>
+        <v>923.8787878787331</v>
       </c>
       <c r="V44" t="n">
-        <v>627.6799913913483</v>
+        <v>611.7575757574689</v>
       </c>
       <c r="W44" t="n">
-        <v>627.6799913913483</v>
+        <v>334.0955893542098</v>
       </c>
       <c r="X44" t="n">
-        <v>627.6799913913483</v>
+        <v>24.72</v>
       </c>
       <c r="Y44" t="n">
-        <v>627.6799913913483</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>359.0704628190657</v>
+        <v>314.4924063890996</v>
       </c>
       <c r="C45" t="n">
-        <v>283.2119653993493</v>
+        <v>238.6339089693831</v>
       </c>
       <c r="D45" t="n">
-        <v>220.6486453006597</v>
+        <v>176.0705888706936</v>
       </c>
       <c r="E45" t="n">
-        <v>163.4041026522631</v>
+        <v>118.826046222297</v>
       </c>
       <c r="F45" t="n">
-        <v>109.2260800887511</v>
+        <v>64.64802365878504</v>
       </c>
       <c r="G45" t="n">
-        <v>69.2980564299661</v>
+        <v>24.72</v>
       </c>
       <c r="H45" t="n">
         <v>24.72</v>
@@ -7718,22 +7718,22 @@
         <v>24.72</v>
       </c>
       <c r="J45" t="n">
-        <v>168.3926316847329</v>
+        <v>24.72</v>
       </c>
       <c r="K45" t="n">
-        <v>391.2834226847767</v>
+        <v>247.6107910000438</v>
       </c>
       <c r="L45" t="n">
-        <v>620.7940963054763</v>
+        <v>553.5207910000438</v>
       </c>
       <c r="M45" t="n">
-        <v>759.7505380483354</v>
+        <v>692.477232742903</v>
       </c>
       <c r="N45" t="n">
-        <v>947.3061903917528</v>
+        <v>880.0328850863203</v>
       </c>
       <c r="O45" t="n">
-        <v>1236</v>
+        <v>1168.726694694568</v>
       </c>
       <c r="P45" t="n">
         <v>1236</v>
@@ -7742,28 +7742,28 @@
         <v>1236</v>
       </c>
       <c r="R45" t="n">
-        <v>1085.874882069114</v>
+        <v>1236</v>
       </c>
       <c r="S45" t="n">
-        <v>1085.874882069114</v>
+        <v>1176.511713967822</v>
       </c>
       <c r="T45" t="n">
-        <v>966.1697066064072</v>
+        <v>1056.806538505115</v>
       </c>
       <c r="U45" t="n">
-        <v>850.8197148532169</v>
+        <v>941.456546751925</v>
       </c>
       <c r="V45" t="n">
-        <v>721.0109601143076</v>
+        <v>811.6477920130158</v>
       </c>
       <c r="W45" t="n">
-        <v>573.1593006094304</v>
+        <v>663.7961325081385</v>
       </c>
       <c r="X45" t="n">
-        <v>573.1593006094304</v>
+        <v>528.5812441794642</v>
       </c>
       <c r="Y45" t="n">
-        <v>458.6225402395976</v>
+        <v>414.0444838096315</v>
       </c>
     </row>
     <row r="46">
@@ -7803,25 +7803,25 @@
         <v>938.5098213509521</v>
       </c>
       <c r="L46" t="n">
-        <v>938.5098213509521</v>
+        <v>826.1118528524502</v>
       </c>
       <c r="M46" t="n">
-        <v>938.5098213509521</v>
+        <v>826.1118528524502</v>
       </c>
       <c r="N46" t="n">
-        <v>677.7604325188146</v>
+        <v>826.1118528524502</v>
       </c>
       <c r="O46" t="n">
-        <v>365.6392203974804</v>
+        <v>722.9964739508409</v>
       </c>
       <c r="P46" t="n">
-        <v>53.51800827614801</v>
+        <v>410.8752618294893</v>
       </c>
       <c r="Q46" t="n">
-        <v>24.72</v>
+        <v>410.8752618294893</v>
       </c>
       <c r="R46" t="n">
-        <v>24.72</v>
+        <v>98.75404970813348</v>
       </c>
       <c r="S46" t="n">
         <v>24.72</v>
@@ -7964,10 +7964,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>1.605307752628015</v>
+        <v>341.6053077526281</v>
       </c>
       <c r="K2" t="n">
-        <v>157.6104903234081</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>470.2783727696964</v>
+        <v>287.8888630931045</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8046,7 +8046,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K3" t="n">
-        <v>295.8802408630135</v>
+        <v>176.6784122079271</v>
       </c>
       <c r="L3" t="n">
         <v>388.0893364597981</v>
@@ -8061,7 +8061,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P3" t="n">
-        <v>99.94888318546316</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8204,10 +8204,10 @@
         <v>1.605307752628015</v>
       </c>
       <c r="K5" t="n">
-        <v>219.7818873083327</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>277.8286030150754</v>
+        <v>157.6104903234081</v>
       </c>
       <c r="M5" t="n">
         <v>815.08446935086</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>130.2783727696965</v>
+        <v>470.2783727696964</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8283,7 +8283,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K6" t="n">
-        <v>176.6784122079271</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L6" t="n">
         <v>388.0893364597981</v>
@@ -8298,7 +8298,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P6" t="n">
-        <v>219.1507118405495</v>
+        <v>99.94888318546316</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>173.9236216365394</v>
+        <v>294.8286030150754</v>
       </c>
       <c r="M8" t="n">
         <v>832.08446935086</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>487.2783727696964</v>
+        <v>366.3733913911605</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8520,7 +8520,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>295.8802408630135</v>
+        <v>243.9915435210584</v>
       </c>
       <c r="L9" t="n">
         <v>388.0893364597981</v>
@@ -8535,7 +8535,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
-        <v>167.2620144985943</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>371.6053077526371</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>186.3983691113159</v>
       </c>
       <c r="M11" t="n">
-        <v>845.0844693508692</v>
+        <v>845.0844693508678</v>
       </c>
       <c r="N11" t="n">
-        <v>776.9519329442162</v>
+        <v>776.9519329442148</v>
       </c>
       <c r="O11" t="n">
         <v>3.868382136906519</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>316.676741881021</v>
+        <v>500.2783727697043</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8766,10 +8766,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N12" t="n">
-        <v>484.9945773042078</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O12" t="n">
-        <v>382.6817988009037</v>
+        <v>382.2678489337484</v>
       </c>
       <c r="P12" t="n">
         <v>219.1507118405495</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>371.6053077526353</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K14" t="n">
-        <v>319.8855577889612</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>307.8286030150917</v>
+        <v>186.3983691113167</v>
       </c>
       <c r="M14" t="n">
-        <v>773.7686776581444</v>
+        <v>845.0844693508675</v>
       </c>
       <c r="N14" t="n">
-        <v>406.9519329442071</v>
+        <v>776.9519329442146</v>
       </c>
       <c r="O14" t="n">
         <v>3.868382136906519</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>130.2783727696965</v>
+        <v>500.2783727697039</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9006,7 +9006,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O15" t="n">
-        <v>382.2678489337537</v>
+        <v>382.2678489337484</v>
       </c>
       <c r="P15" t="n">
         <v>219.1507118405495</v>
@@ -9149,16 +9149,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>1.605307752628015</v>
+        <v>371.6053077526356</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>186.3983691113235</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>845.0844693508674</v>
+        <v>661.4828384621767</v>
       </c>
       <c r="N17" t="n">
         <v>776.9519329442146</v>
@@ -9243,7 +9243,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>382.2678489337546</v>
+        <v>382.2678489337484</v>
       </c>
       <c r="P18" t="n">
         <v>219.1507118405495</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>1.605307752628015</v>
+        <v>371.6053077526356</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>186.3983691113164</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>845.0844693508675</v>
       </c>
       <c r="N20" t="n">
-        <v>776.9519329442146</v>
+        <v>593.3503020555165</v>
       </c>
       <c r="O20" t="n">
         <v>3.868382136906519</v>
@@ -9480,7 +9480,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O21" t="n">
-        <v>382.2678489337611</v>
+        <v>382.2678489337484</v>
       </c>
       <c r="P21" t="n">
         <v>219.1507118405495</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>1.605307752628015</v>
+        <v>371.6053077526358</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>307.8286030150918</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>845.0844693508687</v>
+        <v>845.0844693508677</v>
       </c>
       <c r="N23" t="n">
-        <v>655.5216990404499</v>
+        <v>776.9519329442148</v>
       </c>
       <c r="O23" t="n">
         <v>3.868382136906519</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>500.2783727697052</v>
+        <v>316.676741881006</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9717,7 +9717,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O24" t="n">
-        <v>382.2678489337611</v>
+        <v>382.2678489337484</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9866,22 +9866,22 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>156.650894363841</v>
       </c>
       <c r="M26" t="n">
-        <v>814.0844693508842</v>
+        <v>814.084469350871</v>
       </c>
       <c r="N26" t="n">
-        <v>563.6028273080689</v>
+        <v>745.951932944218</v>
       </c>
       <c r="O26" t="n">
-        <v>342.8683821369307</v>
+        <v>3.868382136906519</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>469.2783727697206</v>
+        <v>469.2783727697075</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,7 +9939,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>104.3033173132281</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
         <v>295.8802408630135</v>
@@ -9957,7 +9957,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P27" t="n">
-        <v>219.1507118405495</v>
+        <v>95.9892872259289</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>340.6053077526418</v>
+        <v>340.6053077526371</v>
       </c>
       <c r="K29" t="n">
-        <v>156.6508943638358</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>814.0844693508737</v>
+        <v>814.0844693508692</v>
       </c>
       <c r="N29" t="n">
-        <v>745.951932944221</v>
+        <v>563.6028273080499</v>
       </c>
       <c r="O29" t="n">
         <v>3.868382136906519</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>130.2783727696965</v>
+        <v>469.2783727697056</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10194,7 +10194,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P30" t="n">
-        <v>95.98928722593212</v>
+        <v>95.98928722592524</v>
       </c>
       <c r="Q30" t="n">
         <v>17.27519534353338</v>
@@ -10340,22 +10340,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>140.3377630506965</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>797.0844693508765</v>
+        <v>797.0844693508732</v>
       </c>
       <c r="N32" t="n">
-        <v>728.9519329442235</v>
+        <v>728.9519329442203</v>
       </c>
       <c r="O32" t="n">
-        <v>3.868382136906519</v>
+        <v>325.8683821369196</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>452.2783727697129</v>
+        <v>270.6161358203902</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10413,13 +10413,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>227.4647419277884</v>
+        <v>82.34087153916931</v>
       </c>
       <c r="K33" t="n">
-        <v>295.8802408630135</v>
+        <v>250.5295553238712</v>
       </c>
       <c r="L33" t="n">
-        <v>351.5328982542499</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M33" t="n">
         <v>471.6948204301074</v>
@@ -10431,7 +10431,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P33" t="n">
-        <v>65.23259411834908</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10571,19 +10571,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>310.6053077526281</v>
+        <v>1.605307752628015</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>258.8855577889447</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>602.9474849267932</v>
+        <v>784.08446935086</v>
       </c>
       <c r="N35" t="n">
-        <v>715.9519329442071</v>
+        <v>584.9293907311956</v>
       </c>
       <c r="O35" t="n">
         <v>3.868382136906519</v>
@@ -10650,13 +10650,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>227.4647419277884</v>
+        <v>150.2937051810203</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>300.0581507794373</v>
+        <v>377.2291875262055</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10808,16 +10808,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>1.605307752628015</v>
+        <v>310.6053077526281</v>
       </c>
       <c r="K38" t="n">
-        <v>258.8855577889447</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>653.0619271378484</v>
+        <v>602.9474849267932</v>
       </c>
       <c r="N38" t="n">
         <v>715.9519329442071</v>
@@ -10887,7 +10887,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>227.4647419277884</v>
+        <v>82.34087153916931</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
@@ -10896,7 +10896,7 @@
         <v>377.2291875262055</v>
       </c>
       <c r="M39" t="n">
-        <v>394.5237836833392</v>
+        <v>385.729536349758</v>
       </c>
       <c r="N39" t="n">
         <v>485.4085271713503</v>
@@ -10905,7 +10905,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P39" t="n">
-        <v>65.23259411834908</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11124,19 +11124,19 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>82.34087153916931</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>377.2291875262055</v>
+        <v>335.5901869394767</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>399.4432430910009</v>
+        <v>295.9583732891105</v>
       </c>
       <c r="O42" t="n">
         <v>382.6817988009037</v>
@@ -11288,16 +11288,16 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>127.8630155759333</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>784.08446935086</v>
       </c>
       <c r="N44" t="n">
-        <v>715.9519329442071</v>
+        <v>534.8149485201404</v>
       </c>
       <c r="O44" t="n">
-        <v>3.868382136906519</v>
+        <v>312.8683821369065</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -11361,13 +11361,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>227.4647419277884</v>
+        <v>82.34087153916931</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>300.0581507794373</v>
+        <v>377.2291875262055</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -11379,7 +11379,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P45" t="n">
-        <v>65.23259411834908</v>
+        <v>133.1854277602</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22512,10 +22512,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.17615076644779</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>44.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -22566,7 +22566,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>19.7015725234539</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -23229,19 +23229,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>52.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>46.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>45.36340243776998</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>45.97491498493444</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23277,13 +23277,13 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>226.9509787134885</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>103.5413836236691</v>
       </c>
       <c r="V11" t="n">
-        <v>258.4588519505967</v>
+        <v>271.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>153.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23423,13 +23423,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>203.688055891906</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>203.6880558918933</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1.293709211052157</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>19.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>19.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>18.36340243776998</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.029005352717506</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>199.9509787134885</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -23523,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>185.090468189101</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.414067078383653</v>
+        <v>2.414067078388996</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3433865039687634</v>
+        <v>0.3433865039815625</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3433865039817476</v>
+        <v>0.3433865039815345</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.3433865039815625</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3433865039691568</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24411,7 +24411,7 @@
         <v>169.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>137.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>91.36340243776998</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24459,19 +24459,19 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>173.8705798626244</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>337.189778960671</v>
+        <v>299.3127289862063</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>68.51467033857506</v>
+        <v>326.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>280.2818334606677</v>
@@ -24599,22 +24599,22 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>180.9297425500909</v>
       </c>
       <c r="N28" t="n">
         <v>232.1418949438161</v>
       </c>
       <c r="O28" t="n">
-        <v>303.4668099806543</v>
+        <v>143.1888129059427</v>
       </c>
       <c r="P28" t="n">
-        <v>35.72600345940941</v>
+        <v>15.07425798400421</v>
       </c>
       <c r="Q28" t="n">
-        <v>60.04126642557378</v>
+        <v>60.04126642558697</v>
       </c>
       <c r="R28" t="n">
-        <v>67.6560951942416</v>
+        <v>67.65609519425479</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24648,22 +24648,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>137.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>92.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>92.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>91.36340243776998</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>91.97491498493444</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,16 +24702,16 @@
         <v>272.9509787134885</v>
       </c>
       <c r="U29" t="n">
-        <v>337.189778960671</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>317.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>76.57103498660615</v>
+        <v>321.6937703003713</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>280.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24833,25 +24833,25 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>85.27398881351688</v>
       </c>
       <c r="M31" t="n">
         <v>180.9297425500909</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>232.1418949438161</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>15.07425798400137</v>
+        <v>25.69537286537417</v>
       </c>
       <c r="Q31" t="n">
-        <v>60.04126642558413</v>
+        <v>60.04126642558879</v>
       </c>
       <c r="R31" t="n">
-        <v>395.693093832967</v>
+        <v>67.65609519425661</v>
       </c>
       <c r="S31" t="n">
         <v>47.29370921105216</v>
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.691395026534281</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -24936,7 +24936,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.691395026546843</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -25593,19 +25593,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>168.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>136.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>97.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>91.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1.060746130899247</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -25650,19 +25650,19 @@
         <v>271.9509787134885</v>
       </c>
       <c r="U41" t="n">
-        <v>336.189778960671</v>
+        <v>27.18977896060767</v>
       </c>
       <c r="V41" t="n">
-        <v>7.851024166763864</v>
+        <v>7.851024166764091</v>
       </c>
       <c r="W41" t="n">
-        <v>264.4534130968231</v>
+        <v>16.37347598088775</v>
       </c>
       <c r="X41" t="n">
         <v>279.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>198.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25781,10 +25781,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>84.27398881351688</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>179.9297425500909</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -25793,16 +25793,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>44.07425798389966</v>
+        <v>44.07425798388897</v>
       </c>
       <c r="Q43" t="n">
-        <v>351.9802119248437</v>
+        <v>89.04126642547203</v>
       </c>
       <c r="R43" t="n">
-        <v>405.6560951942658</v>
+        <v>358.0976001189884</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>46.29370921105216</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25836,19 +25836,19 @@
         <v>163.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>124.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>118.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>118.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>117.36340243777</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>117.9749149849345</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25884,19 +25884,19 @@
         <v>199.8705798626244</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>298.9509787134886</v>
       </c>
       <c r="U44" t="n">
-        <v>59.90394915159442</v>
+        <v>54.18977896061676</v>
       </c>
       <c r="V44" t="n">
-        <v>343.8510241668239</v>
+        <v>34.85102416677228</v>
       </c>
       <c r="W44" t="n">
-        <v>352.3734759809475</v>
+        <v>77.48810944172101</v>
       </c>
       <c r="X44" t="n">
-        <v>306.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>225.3174326828064</v>
@@ -25927,7 +25927,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>44.13227586566643</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>99.56230789929285</v>
+        <v>248.1861746508698</v>
       </c>
       <c r="S45" t="n">
-        <v>176.6486226061207</v>
+        <v>117.7552194342648</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25975,7 +25975,7 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>133.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -26018,28 +26018,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>111.2739888135169</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>206.9297425500909</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>258.1418949438161</v>
       </c>
       <c r="O46" t="n">
-        <v>20.46680998053341</v>
+        <v>227.3825848680611</v>
       </c>
       <c r="P46" t="n">
-        <v>71.07425798389613</v>
+        <v>71.07425798387715</v>
       </c>
       <c r="Q46" t="n">
-        <v>396.5312382322115</v>
+        <v>425.041266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>432.6560951942658</v>
+        <v>123.6560951941236</v>
       </c>
       <c r="S46" t="n">
-        <v>73.29370921105215</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3256267.296479515</v>
+        <v>3256267.296479514</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4031996.542370435</v>
+        <v>4031996.542370434</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4819090.109099735</v>
+        <v>4819090.109099732</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5606183.675829031</v>
+        <v>5606183.675829028</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6393277.242558327</v>
+        <v>6393277.242558324</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7095172.828073936</v>
+        <v>7095172.828073927</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7803807.249953173</v>
+        <v>7803807.249953168</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8587088.512349382</v>
+        <v>8587088.512349376</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9371373.198920893</v>
+        <v>9371373.198920887</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10158483.84912877</v>
+        <v>10158483.84912876</v>
       </c>
     </row>
     <row r="15">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11524977.82907615</v>
+        <v>11524977.82907616</v>
       </c>
     </row>
   </sheetData>
@@ -26278,34 +26278,34 @@
         <v>1416799.170374169</v>
       </c>
       <c r="E2" t="n">
-        <v>1357324.812454959</v>
+        <v>1357324.812454958</v>
       </c>
       <c r="F2" t="n">
         <v>1396312.642603657</v>
       </c>
       <c r="G2" t="n">
-        <v>1416768.420112739</v>
+        <v>1416768.420112738</v>
       </c>
       <c r="H2" t="n">
         <v>1416768.420112738</v>
       </c>
       <c r="I2" t="n">
-        <v>1416768.420112739</v>
+        <v>1416768.420112738</v>
       </c>
       <c r="J2" t="n">
-        <v>1275541.959382644</v>
+        <v>1275541.959382639</v>
       </c>
       <c r="K2" t="n">
-        <v>1275541.959382639</v>
+        <v>1275541.959382638</v>
       </c>
       <c r="L2" t="n">
-        <v>1416558.155949543</v>
+        <v>1416558.155949542</v>
       </c>
       <c r="M2" t="n">
         <v>1416799.170374169</v>
       </c>
       <c r="N2" t="n">
-        <v>1416799.17037417</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="O2" t="n">
         <v>1263355.556758299</v>
@@ -26330,7 +26330,7 @@
         <v>5984</v>
       </c>
       <c r="E3" t="n">
-        <v>286976.0000000058</v>
+        <v>286976.0000000047</v>
       </c>
       <c r="F3" t="n">
         <v>21600</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>651796.2917931571</v>
+        <v>651781.8831196837</v>
       </c>
       <c r="C4" t="n">
-        <v>649761.3922393247</v>
+        <v>649746.9835658516</v>
       </c>
       <c r="D4" t="n">
-        <v>649849.7250775925</v>
+        <v>649834.9380406409</v>
       </c>
       <c r="E4" t="n">
-        <v>617348.8314872442</v>
+        <v>617333.7551135145</v>
       </c>
       <c r="F4" t="n">
-        <v>634984.6878487428</v>
+        <v>634969.6114750134</v>
       </c>
       <c r="G4" t="n">
-        <v>643180.6430225902</v>
+        <v>643165.5666488607</v>
       </c>
       <c r="H4" t="n">
-        <v>641152.8235864372</v>
+        <v>641137.7472127082</v>
       </c>
       <c r="I4" t="n">
-        <v>639122.1732814389</v>
+        <v>639107.0969077095</v>
       </c>
       <c r="J4" t="n">
-        <v>568688.4647812612</v>
+        <v>568674.078364461</v>
       </c>
       <c r="K4" t="n">
-        <v>566909.6951240634</v>
+        <v>566895.3087072651</v>
       </c>
       <c r="L4" t="n">
-        <v>634651.1358526046</v>
+        <v>634637.1277992844</v>
       </c>
       <c r="M4" t="n">
-        <v>633128.9769891049</v>
+        <v>633115.2582725624</v>
       </c>
       <c r="N4" t="n">
-        <v>631016.5683353457</v>
+        <v>631002.8496188035</v>
       </c>
       <c r="O4" t="n">
-        <v>554865.0720165286</v>
+        <v>554851.3532999863</v>
       </c>
       <c r="P4" t="n">
-        <v>520778.7645587707</v>
+        <v>520765.0458422284</v>
       </c>
     </row>
     <row r="5">
@@ -26434,28 +26434,28 @@
         <v>57889.945</v>
       </c>
       <c r="E5" t="n">
-        <v>54729.102000001</v>
+        <v>54729.1020000008</v>
       </c>
       <c r="F5" t="n">
-        <v>56998.965000001</v>
+        <v>56998.9650000008</v>
       </c>
       <c r="G5" t="n">
-        <v>58344.069000001</v>
+        <v>58344.0690000008</v>
       </c>
       <c r="H5" t="n">
-        <v>58344.069000001</v>
+        <v>58344.0690000008</v>
       </c>
       <c r="I5" t="n">
-        <v>58344.069000001</v>
+        <v>58344.0690000008</v>
       </c>
       <c r="J5" t="n">
-        <v>48977.128000001</v>
+        <v>48977.1280000008</v>
       </c>
       <c r="K5" t="n">
-        <v>48977.128000001</v>
+        <v>48977.1280000008</v>
       </c>
       <c r="L5" t="n">
-        <v>56938.911000001</v>
+        <v>56938.91100000081</v>
       </c>
       <c r="M5" t="n">
         <v>56652.925</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>483169.559279877</v>
+        <v>483183.9679533502</v>
       </c>
       <c r="C6" t="n">
-        <v>704434.4588337096</v>
+        <v>704448.8675071823</v>
       </c>
       <c r="D6" t="n">
-        <v>703075.500296577</v>
+        <v>703090.2873335286</v>
       </c>
       <c r="E6" t="n">
-        <v>398270.8789677083</v>
+        <v>398285.9553414383</v>
       </c>
       <c r="F6" t="n">
-        <v>682728.9897549134</v>
+        <v>682744.0661286423</v>
       </c>
       <c r="G6" t="n">
-        <v>698443.7080901479</v>
+        <v>698458.7844638762</v>
       </c>
       <c r="H6" t="n">
-        <v>717271.5275262998</v>
+        <v>717286.6039000289</v>
       </c>
       <c r="I6" t="n">
-        <v>719302.177831299</v>
+        <v>719317.2542050278</v>
       </c>
       <c r="J6" t="n">
-        <v>337908.366601382</v>
+        <v>337922.7530181773</v>
       </c>
       <c r="K6" t="n">
-        <v>638055.1362585749</v>
+        <v>638069.5226753724</v>
       </c>
       <c r="L6" t="n">
-        <v>622568.1090969376</v>
+        <v>622582.1171502569</v>
       </c>
       <c r="M6" t="n">
-        <v>722217.2683850643</v>
+        <v>722230.9871016066</v>
       </c>
       <c r="N6" t="n">
-        <v>729129.677038824</v>
+        <v>729143.3957553655</v>
       </c>
       <c r="O6" t="n">
-        <v>539653.2877417702</v>
+        <v>539667.0064583129</v>
       </c>
       <c r="P6" t="n">
-        <v>630587.5085882021</v>
+        <v>630601.2273047443</v>
       </c>
     </row>
   </sheetData>
@@ -26868,28 +26868,28 @@
         <v>357</v>
       </c>
       <c r="E4" t="n">
-        <v>370.0000000000164</v>
+        <v>370.0000000000132</v>
       </c>
       <c r="F4" t="n">
-        <v>370.0000000000164</v>
+        <v>370.0000000000132</v>
       </c>
       <c r="G4" t="n">
-        <v>370.0000000000164</v>
+        <v>370.0000000000132</v>
       </c>
       <c r="H4" t="n">
-        <v>370.0000000000164</v>
+        <v>370.0000000000132</v>
       </c>
       <c r="I4" t="n">
-        <v>370.0000000000164</v>
+        <v>370.0000000000132</v>
       </c>
       <c r="J4" t="n">
-        <v>339.0000000000164</v>
+        <v>339.0000000000132</v>
       </c>
       <c r="K4" t="n">
-        <v>339.0000000000164</v>
+        <v>339.0000000000132</v>
       </c>
       <c r="L4" t="n">
-        <v>322.0000000000164</v>
+        <v>322.0000000000132</v>
       </c>
       <c r="M4" t="n">
         <v>309</v>
@@ -26990,10 +26990,10 @@
         <v>21</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>264</v>
@@ -27008,7 +27008,7 @@
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>152</v>
@@ -27085,7 +27085,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00000000000933</v>
+        <v>13.00000000000609</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>13.00000000001643</v>
+        <v>13.00000000001319</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27527,7 +27527,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5287434221972</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>330.1322758656664</v>
@@ -27560,19 +27560,19 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>405</v>
+        <v>194.1861746508699</v>
       </c>
       <c r="S3" t="n">
-        <v>122.6486226061207</v>
+        <v>216.4925476889577</v>
       </c>
       <c r="T3" t="n">
-        <v>64.50812370807985</v>
+        <v>404.5081237080798</v>
       </c>
       <c r="U3" t="n">
         <v>400.1964918356584</v>
       </c>
       <c r="V3" t="n">
-        <v>302.5013563115097</v>
+        <v>405</v>
       </c>
       <c r="W3" t="n">
         <v>405</v>
@@ -27591,16 +27591,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>405</v>
+        <v>332.4179250840635</v>
       </c>
       <c r="C4" t="n">
-        <v>405</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>405</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>389.8331614139934</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27618,7 +27618,7 @@
         <v>22.77475211459628</v>
       </c>
       <c r="K4" t="n">
-        <v>267.9889705224545</v>
+        <v>405</v>
       </c>
       <c r="L4" t="n">
         <v>405</v>
@@ -27654,13 +27654,13 @@
         <v>405</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>405</v>
       </c>
       <c r="X4" t="n">
         <v>405</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5">
@@ -27752,10 +27752,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>21.09991244551929</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>7.937686897702633</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.5287434221972</v>
       </c>
       <c r="H6" t="n">
         <v>330.1322758656664</v>
@@ -27797,25 +27797,25 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>405</v>
+        <v>194.1861746508699</v>
       </c>
       <c r="S6" t="n">
         <v>405</v>
       </c>
       <c r="T6" t="n">
-        <v>64.50812370807985</v>
+        <v>404.5081237080798</v>
       </c>
       <c r="U6" t="n">
         <v>400.1964918356584</v>
       </c>
       <c r="V6" t="n">
-        <v>135.8098836182904</v>
+        <v>405</v>
       </c>
       <c r="W6" t="n">
         <v>405</v>
       </c>
       <c r="X6" t="n">
-        <v>405</v>
+        <v>361.0949655452234</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>352.9333158613803</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>405</v>
@@ -27840,25 +27840,25 @@
         <v>405</v>
       </c>
       <c r="F7" t="n">
-        <v>405</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>405</v>
+        <v>244.8671515300546</v>
       </c>
       <c r="H7" t="n">
-        <v>405</v>
+        <v>227.1999129868645</v>
       </c>
       <c r="I7" t="n">
-        <v>405</v>
+        <v>171.3189638168396</v>
       </c>
       <c r="J7" t="n">
-        <v>35.96401379090202</v>
+        <v>22.77475211459628</v>
       </c>
       <c r="K7" t="n">
-        <v>405</v>
+        <v>267.9889705224545</v>
       </c>
       <c r="L7" t="n">
-        <v>405</v>
+        <v>397.2739888135169</v>
       </c>
       <c r="M7" t="n">
         <v>405</v>
@@ -27879,25 +27879,25 @@
         <v>405</v>
       </c>
       <c r="S7" t="n">
-        <v>405</v>
+        <v>359.2937092110521</v>
       </c>
       <c r="T7" t="n">
         <v>405</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9487519301956</v>
+        <v>405</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>405</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>405</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8">
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>47.53972850727888</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28007,7 +28007,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.8688387215372</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>177.1861746508699</v>
+        <v>405</v>
       </c>
       <c r="S9" t="n">
-        <v>172.122480132427</v>
+        <v>405</v>
       </c>
       <c r="T9" t="n">
         <v>404.5081237080798</v>
@@ -28055,7 +28055,7 @@
         <v>405</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>42.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28065,16 +28065,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>405</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>405</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>405</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>405</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>405</v>
@@ -28089,13 +28089,13 @@
         <v>405</v>
       </c>
       <c r="J10" t="n">
-        <v>34.96587821241199</v>
+        <v>266.8324490784892</v>
       </c>
       <c r="K10" t="n">
         <v>405</v>
       </c>
       <c r="L10" t="n">
-        <v>397.2739888135169</v>
+        <v>405</v>
       </c>
       <c r="M10" t="n">
         <v>405</v>
@@ -28122,7 +28122,7 @@
         <v>209.2694845390446</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9487519301956</v>
+        <v>405</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28268,10 +28268,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R12" t="n">
-        <v>241.6107321849519</v>
+        <v>164.1861746508543</v>
       </c>
       <c r="S12" t="n">
         <v>358</v>
@@ -28280,7 +28280,7 @@
         <v>358</v>
       </c>
       <c r="U12" t="n">
-        <v>358</v>
+        <v>289.2527641417439</v>
       </c>
       <c r="V12" t="n">
         <v>358</v>
@@ -28305,7 +28305,7 @@
         <v>358</v>
       </c>
       <c r="C13" t="n">
-        <v>358</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D13" t="n">
         <v>358</v>
@@ -28317,19 +28317,19 @@
         <v>358</v>
       </c>
       <c r="G13" t="n">
-        <v>358</v>
+        <v>244.8671515300546</v>
       </c>
       <c r="H13" t="n">
         <v>358</v>
       </c>
       <c r="I13" t="n">
-        <v>175.845914033442</v>
+        <v>358</v>
       </c>
       <c r="J13" t="n">
-        <v>22.77475211459628</v>
+        <v>358</v>
       </c>
       <c r="K13" t="n">
-        <v>267.9889705224545</v>
+        <v>358</v>
       </c>
       <c r="L13" t="n">
         <v>358</v>
@@ -28362,16 +28362,16 @@
         <v>358</v>
       </c>
       <c r="V13" t="n">
-        <v>358</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W13" t="n">
-        <v>358</v>
+        <v>288.9379299965947</v>
       </c>
       <c r="X13" t="n">
-        <v>358</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y13" t="n">
-        <v>358</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="14">
@@ -28472,7 +28472,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>325.5287434221972</v>
@@ -28508,25 +28508,25 @@
         <v>146.1717933923664</v>
       </c>
       <c r="R15" t="n">
-        <v>164.186174650853</v>
+        <v>385</v>
       </c>
       <c r="S15" t="n">
+        <v>92.64862260610332</v>
+      </c>
+      <c r="T15" t="n">
+        <v>34.50812370807232</v>
+      </c>
+      <c r="U15" t="n">
         <v>385</v>
-      </c>
-      <c r="T15" t="n">
-        <v>34.50812370807249</v>
-      </c>
-      <c r="U15" t="n">
-        <v>247.7232990924942</v>
       </c>
       <c r="V15" t="n">
         <v>385</v>
       </c>
       <c r="W15" t="n">
-        <v>385</v>
+        <v>62.37314290982104</v>
       </c>
       <c r="X15" t="n">
-        <v>385</v>
+        <v>302.2514658895518</v>
       </c>
       <c r="Y15" t="n">
         <v>385</v>
@@ -28542,13 +28542,13 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C16" t="n">
-        <v>385</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D16" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E16" t="n">
-        <v>385</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F16" t="n">
         <v>274.3828559677419</v>
@@ -28590,25 +28590,25 @@
         <v>385</v>
       </c>
       <c r="S16" t="n">
-        <v>385</v>
+        <v>359.2937092110521</v>
       </c>
       <c r="T16" t="n">
-        <v>385</v>
+        <v>244.0547073648524</v>
       </c>
       <c r="U16" t="n">
         <v>150.9487519301956</v>
       </c>
       <c r="V16" t="n">
-        <v>199.1703102162162</v>
+        <v>385</v>
       </c>
       <c r="W16" t="n">
         <v>385</v>
       </c>
       <c r="X16" t="n">
-        <v>285.4189049952328</v>
+        <v>385</v>
       </c>
       <c r="Y16" t="n">
-        <v>287.4653528494624</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17">
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>226.1308902855874</v>
+        <v>226.1308902855809</v>
       </c>
       <c r="S17" t="n">
         <v>401</v>
@@ -28700,7 +28700,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R18" t="n">
         <v>401</v>
@@ -28751,22 +28751,22 @@
         <v>401</v>
       </c>
       <c r="T18" t="n">
-        <v>104.4651763496425</v>
+        <v>401</v>
       </c>
       <c r="U18" t="n">
-        <v>30.19649183565103</v>
+        <v>400.1964918356584</v>
       </c>
       <c r="V18" t="n">
-        <v>401</v>
+        <v>286.9575881565618</v>
       </c>
       <c r="W18" t="n">
-        <v>401</v>
+        <v>62.37314290982104</v>
       </c>
       <c r="X18" t="n">
-        <v>401</v>
+        <v>49.86273944538007</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>29.39139276612687</v>
       </c>
     </row>
     <row r="19">
@@ -28776,37 +28776,37 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>287.1138003370787</v>
+        <v>401</v>
       </c>
       <c r="C19" t="n">
-        <v>272.7252466480447</v>
+        <v>356.4177649753649</v>
       </c>
       <c r="D19" t="n">
-        <v>285.5362180555555</v>
+        <v>401</v>
       </c>
       <c r="E19" t="n">
-        <v>280.9809048369565</v>
+        <v>401</v>
       </c>
       <c r="F19" t="n">
-        <v>274.3828559677419</v>
+        <v>401</v>
       </c>
       <c r="G19" t="n">
-        <v>244.8671515300546</v>
+        <v>401</v>
       </c>
       <c r="H19" t="n">
-        <v>227.1999129868645</v>
+        <v>401</v>
       </c>
       <c r="I19" t="n">
-        <v>171.3189638168396</v>
+        <v>401</v>
       </c>
       <c r="J19" t="n">
-        <v>307.0095055291274</v>
+        <v>22.77475211459628</v>
       </c>
       <c r="K19" t="n">
-        <v>267.9889705224545</v>
+        <v>401</v>
       </c>
       <c r="L19" t="n">
-        <v>397.2739888135169</v>
+        <v>401</v>
       </c>
       <c r="M19" t="n">
         <v>401</v>
@@ -28830,19 +28830,19 @@
         <v>359.2937092110521</v>
       </c>
       <c r="T19" t="n">
-        <v>401</v>
+        <v>209.2694845390446</v>
       </c>
       <c r="U19" t="n">
-        <v>401</v>
+        <v>150.9487519301956</v>
       </c>
       <c r="V19" t="n">
-        <v>401</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W19" t="n">
-        <v>401</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X19" t="n">
-        <v>401</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y19" t="n">
         <v>401</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>226.1308902855809</v>
+        <v>226.1308902855883</v>
       </c>
       <c r="S20" t="n">
         <v>401</v>
@@ -28943,10 +28943,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>325.5287434221972</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>146.1717933923664</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>401</v>
@@ -28988,19 +28988,19 @@
         <v>401</v>
       </c>
       <c r="T21" t="n">
-        <v>119.3706487930696</v>
+        <v>290.8606959887665</v>
       </c>
       <c r="U21" t="n">
         <v>400.1964918356584</v>
       </c>
       <c r="V21" t="n">
-        <v>401</v>
+        <v>44.51066719151268</v>
       </c>
       <c r="W21" t="n">
         <v>401</v>
       </c>
       <c r="X21" t="n">
-        <v>401</v>
+        <v>49.86273944538007</v>
       </c>
       <c r="Y21" t="n">
         <v>399.3913927661343</v>
@@ -29013,10 +29013,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>384.3600139477954</v>
+        <v>401</v>
       </c>
       <c r="C22" t="n">
-        <v>272.7252466480447</v>
+        <v>401</v>
       </c>
       <c r="D22" t="n">
         <v>401</v>
@@ -29031,19 +29031,19 @@
         <v>244.8671515300546</v>
       </c>
       <c r="H22" t="n">
-        <v>401</v>
+        <v>227.1999129868645</v>
       </c>
       <c r="I22" t="n">
-        <v>401</v>
+        <v>171.3189638168396</v>
       </c>
       <c r="J22" t="n">
         <v>392.7747521146038</v>
       </c>
       <c r="K22" t="n">
-        <v>401</v>
+        <v>267.9889705224545</v>
       </c>
       <c r="L22" t="n">
-        <v>401</v>
+        <v>397.2739888135169</v>
       </c>
       <c r="M22" t="n">
         <v>401</v>
@@ -29073,13 +29073,13 @@
         <v>150.9487519301956</v>
       </c>
       <c r="V22" t="n">
-        <v>199.1703102162162</v>
+        <v>266.290189941198</v>
       </c>
       <c r="W22" t="n">
-        <v>226.3728098387097</v>
+        <v>401</v>
       </c>
       <c r="X22" t="n">
-        <v>247.4436454301076</v>
+        <v>401</v>
       </c>
       <c r="Y22" t="n">
         <v>287.4653528494624</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>226.1308902855809</v>
+        <v>226.1308902855874</v>
       </c>
       <c r="S23" t="n">
         <v>401</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>14.55655664631885</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>239.6017225170721</v>
       </c>
       <c r="G24" t="n">
         <v>325.5287434221972</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.611290361601476</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R24" t="n">
         <v>401</v>
@@ -29250,13 +29250,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>388.1680766653085</v>
+        <v>401</v>
       </c>
       <c r="C25" t="n">
         <v>401</v>
       </c>
       <c r="D25" t="n">
-        <v>285.5362180555555</v>
+        <v>401</v>
       </c>
       <c r="E25" t="n">
         <v>401</v>
@@ -29265,10 +29265,10 @@
         <v>401</v>
       </c>
       <c r="G25" t="n">
-        <v>244.8671515300546</v>
+        <v>401</v>
       </c>
       <c r="H25" t="n">
-        <v>227.1999129868645</v>
+        <v>401</v>
       </c>
       <c r="I25" t="n">
         <v>171.3189638168396</v>
@@ -29277,10 +29277,10 @@
         <v>22.77475211459628</v>
       </c>
       <c r="K25" t="n">
-        <v>267.9889705224545</v>
+        <v>401</v>
       </c>
       <c r="L25" t="n">
-        <v>397.2739888135169</v>
+        <v>401</v>
       </c>
       <c r="M25" t="n">
         <v>401</v>
@@ -29301,22 +29301,22 @@
         <v>401</v>
       </c>
       <c r="S25" t="n">
-        <v>359.2937092110521</v>
+        <v>401</v>
       </c>
       <c r="T25" t="n">
         <v>209.2694845390446</v>
       </c>
       <c r="U25" t="n">
-        <v>401</v>
+        <v>150.9487519301956</v>
       </c>
       <c r="V25" t="n">
-        <v>401</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W25" t="n">
-        <v>401</v>
+        <v>369.7653202082871</v>
       </c>
       <c r="X25" t="n">
-        <v>401</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y25" t="n">
         <v>401</v>
@@ -29429,7 +29429,7 @@
         <v>312</v>
       </c>
       <c r="I27" t="n">
-        <v>209.8688387215372</v>
+        <v>113.5185086722779</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>49.82146334304804</v>
+        <v>146.1717933923664</v>
       </c>
       <c r="R27" t="n">
         <v>312</v>
@@ -29651,7 +29651,7 @@
         <v>312</v>
       </c>
       <c r="D30" t="n">
-        <v>215.6496699507373</v>
+        <v>312</v>
       </c>
       <c r="E30" t="n">
         <v>312</v>
@@ -29699,7 +29699,7 @@
         <v>312</v>
       </c>
       <c r="T30" t="n">
-        <v>312</v>
+        <v>215.6496699507442</v>
       </c>
       <c r="U30" t="n">
         <v>312</v>
@@ -29903,7 +29903,7 @@
         <v>330.1322758656664</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>209.8688387215372</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29930,13 +29930,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>212.1861746508534</v>
+        <v>410.1135109530532</v>
       </c>
       <c r="S33" t="n">
-        <v>227.3075370752097</v>
+        <v>140.6486226061076</v>
       </c>
       <c r="T33" t="n">
-        <v>82.50812370806342</v>
+        <v>82.50812370806666</v>
       </c>
       <c r="U33" t="n">
         <v>400.1964918356584</v>
@@ -29948,7 +29948,7 @@
         <v>419</v>
       </c>
       <c r="X33" t="n">
-        <v>419</v>
+        <v>97.86273944537436</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -29961,34 +29961,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>419</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C34" t="n">
-        <v>419</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D34" t="n">
-        <v>419</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E34" t="n">
         <v>419</v>
       </c>
       <c r="F34" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G34" t="n">
         <v>419</v>
-      </c>
-      <c r="G34" t="n">
-        <v>244.8671515300546</v>
       </c>
       <c r="H34" t="n">
         <v>419</v>
       </c>
       <c r="I34" t="n">
-        <v>219.8124508873987</v>
+        <v>419</v>
       </c>
       <c r="J34" t="n">
         <v>22.77475211459628</v>
       </c>
       <c r="K34" t="n">
-        <v>267.9889705224545</v>
+        <v>419</v>
       </c>
       <c r="L34" t="n">
         <v>419</v>
@@ -30012,10 +30012,10 @@
         <v>419</v>
       </c>
       <c r="S34" t="n">
-        <v>359.2937092110521</v>
+        <v>419</v>
       </c>
       <c r="T34" t="n">
-        <v>209.2694845390446</v>
+        <v>353.0300002514762</v>
       </c>
       <c r="U34" t="n">
         <v>150.9487519301956</v>
@@ -30027,7 +30027,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X34" t="n">
-        <v>419</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y34" t="n">
         <v>419</v>
@@ -30061,7 +30061,7 @@
         <v>403.9749149849345</v>
       </c>
       <c r="I35" t="n">
-        <v>134.0344320962171</v>
+        <v>134.8926370696193</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>226.1308902855809</v>
+        <v>225.2726853121787</v>
       </c>
       <c r="S35" t="n">
         <v>425</v>
@@ -30122,7 +30122,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>52.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30131,13 +30131,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>30.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.5287434221972</v>
       </c>
       <c r="H36" t="n">
-        <v>259.2136481463892</v>
+        <v>21.13227586566641</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -30167,7 +30167,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>425</v>
+        <v>346.7082293708943</v>
       </c>
       <c r="S36" t="n">
         <v>425</v>
@@ -30182,7 +30182,7 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>425</v>
+        <v>123.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>419.8627394453875</v>
@@ -30201,34 +30201,34 @@
         <v>425</v>
       </c>
       <c r="C37" t="n">
-        <v>425</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D37" t="n">
         <v>425</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>425</v>
       </c>
       <c r="F37" t="n">
-        <v>425</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
         <v>244.8671515300546</v>
       </c>
       <c r="H37" t="n">
-        <v>425</v>
+        <v>227.1999129868645</v>
       </c>
       <c r="I37" t="n">
-        <v>341.8663650656958</v>
+        <v>171.3189638168396</v>
       </c>
       <c r="J37" t="n">
         <v>22.77475211459628</v>
       </c>
       <c r="K37" t="n">
-        <v>267.9889705224545</v>
+        <v>425</v>
       </c>
       <c r="L37" t="n">
-        <v>397.2739888135169</v>
+        <v>425</v>
       </c>
       <c r="M37" t="n">
         <v>425</v>
@@ -30249,25 +30249,25 @@
         <v>425</v>
       </c>
       <c r="S37" t="n">
-        <v>359.2937092110521</v>
+        <v>425</v>
       </c>
       <c r="T37" t="n">
         <v>209.2694845390446</v>
       </c>
       <c r="U37" t="n">
-        <v>425</v>
+        <v>365.6151217183571</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>425</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>425</v>
       </c>
     </row>
     <row r="38">
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>225.2726853121787</v>
+        <v>226.1308902855809</v>
       </c>
       <c r="S38" t="n">
         <v>425</v>
@@ -30334,7 +30334,7 @@
         <v>425</v>
       </c>
       <c r="U38" t="n">
-        <v>425</v>
+        <v>424.1417950265978</v>
       </c>
       <c r="V38" t="n">
         <v>425</v>
@@ -30359,16 +30359,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>52.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>67.15022045688823</v>
+        <v>38.93768689770263</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>30.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>325.5287434221972</v>
@@ -30377,7 +30377,7 @@
         <v>330.1322758656664</v>
       </c>
       <c r="I39" t="n">
-        <v>209.8688387215372</v>
+        <v>91.24657502373221</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30404,10 +30404,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>425</v>
+        <v>225.1861746508699</v>
       </c>
       <c r="S39" t="n">
-        <v>425</v>
+        <v>153.6486226061207</v>
       </c>
       <c r="T39" t="n">
         <v>404.5081237080798</v>
@@ -30447,10 +30447,10 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>371.6724589608472</v>
       </c>
       <c r="G40" t="n">
-        <v>275.8015486733979</v>
+        <v>425</v>
       </c>
       <c r="H40" t="n">
         <v>425</v>
@@ -30459,7 +30459,7 @@
         <v>425</v>
       </c>
       <c r="J40" t="n">
-        <v>22.77475211459628</v>
+        <v>331.7747521145963</v>
       </c>
       <c r="K40" t="n">
         <v>425</v>
@@ -30486,13 +30486,13 @@
         <v>425</v>
       </c>
       <c r="S40" t="n">
-        <v>425</v>
+        <v>359.2937092110521</v>
       </c>
       <c r="T40" t="n">
-        <v>425</v>
+        <v>209.2694845390446</v>
       </c>
       <c r="U40" t="n">
-        <v>425</v>
+        <v>150.9487519301956</v>
       </c>
       <c r="V40" t="n">
         <v>199.1703102162162</v>
@@ -30696,7 +30696,7 @@
         <v>313</v>
       </c>
       <c r="J43" t="n">
-        <v>184.0742831350742</v>
+        <v>313</v>
       </c>
       <c r="K43" t="n">
         <v>313</v>
@@ -30726,10 +30726,10 @@
         <v>313</v>
       </c>
       <c r="T43" t="n">
-        <v>313</v>
+        <v>209.2694845390446</v>
       </c>
       <c r="U43" t="n">
-        <v>313</v>
+        <v>287.8047985960297</v>
       </c>
       <c r="V43" t="n">
         <v>313</v>
@@ -34743,10 +34743,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>207.7249325344634</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L2" t="n">
         <v>62.17139698492463</v>
@@ -34764,7 +34764,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q2" t="n">
-        <v>340</v>
+        <v>157.610490323408</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34825,7 +34825,7 @@
         <v>145.1238703886191</v>
       </c>
       <c r="K3" t="n">
-        <v>225.1422131313574</v>
+        <v>105.940384476271</v>
       </c>
       <c r="L3" t="n">
         <v>319.8601489335927</v>
@@ -34840,7 +34840,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P3" t="n">
-        <v>34.71628906711408</v>
+        <v>153.9181177222004</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,16 +34877,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>117.8861996629213</v>
+        <v>45.30412474698482</v>
       </c>
       <c r="C4" t="n">
-        <v>132.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>119.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>108.8522565770369</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34904,7 +34904,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>137.0110294775455</v>
       </c>
       <c r="L4" t="n">
         <v>7.726011186483106</v>
@@ -34940,13 +34940,13 @@
         <v>205.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>178.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>157.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>117.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34983,10 +34983,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>269.896329519388</v>
+        <v>50.11444221105528</v>
       </c>
       <c r="L5" t="n">
-        <v>340</v>
+        <v>219.7818873083327</v>
       </c>
       <c r="M5" t="n">
         <v>340</v>
@@ -35001,7 +35001,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35062,7 +35062,7 @@
         <v>145.1238703886191</v>
       </c>
       <c r="K6" t="n">
-        <v>105.940384476271</v>
+        <v>225.1422131313574</v>
       </c>
       <c r="L6" t="n">
         <v>319.8601489335927</v>
@@ -35077,7 +35077,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P6" t="n">
-        <v>153.9181177222004</v>
+        <v>34.71628906711408</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>65.81951552430158</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>132.2747533519553</v>
       </c>
       <c r="D7" t="n">
         <v>119.4637819444445</v>
@@ -35126,25 +35126,25 @@
         <v>124.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>130.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>160.1328484699454</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>177.8000870131355</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>233.6810361831604</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>13.18926167630574</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>137.0110294775455</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7.726011186483106</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>45.70629078894785</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>195.7305154609554</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>254.0512480698044</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>178.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>157.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>117.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35223,7 +35223,7 @@
         <v>50.11444221105528</v>
       </c>
       <c r="L8" t="n">
-        <v>236.095018621464</v>
+        <v>357</v>
       </c>
       <c r="M8" t="n">
         <v>357</v>
@@ -35238,7 +35238,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q8" t="n">
-        <v>357</v>
+        <v>236.095018621464</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35299,7 +35299,7 @@
         <v>145.1238703886191</v>
       </c>
       <c r="K9" t="n">
-        <v>225.1422131313574</v>
+        <v>173.2535157894023</v>
       </c>
       <c r="L9" t="n">
         <v>319.8601489335927</v>
@@ -35314,7 +35314,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P9" t="n">
-        <v>102.0294203802453</v>
+        <v>153.9181177222004</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,16 +35351,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>132.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>119.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>124.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>130.6171440322581</v>
@@ -35375,13 +35375,13 @@
         <v>233.6810361831604</v>
       </c>
       <c r="J10" t="n">
-        <v>12.1911260978157</v>
+        <v>244.0576969638929</v>
       </c>
       <c r="K10" t="n">
         <v>137.0110294775455</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.726011186483106</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,7 +35408,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>254.0512480698044</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>370.0000000000092</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>50.11444221105529</v>
+        <v>50.11444221105527</v>
       </c>
       <c r="L11" t="n">
-        <v>62.17139698492468</v>
+        <v>248.5697660962406</v>
       </c>
       <c r="M11" t="n">
-        <v>370.0000000000092</v>
+        <v>370.0000000000078</v>
       </c>
       <c r="N11" t="n">
-        <v>370.0000000000092</v>
+        <v>370.0000000000078</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35475,7 +35475,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q11" t="n">
-        <v>186.3983691113245</v>
+        <v>370.0000000000078</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35545,10 +35545,10 @@
         <v>140.3600421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>189.0362040150972</v>
+        <v>189.4501538822398</v>
       </c>
       <c r="O12" t="n">
-        <v>291.6099086951992</v>
+        <v>291.195958828044</v>
       </c>
       <c r="P12" t="n">
         <v>153.9181177222004</v>
@@ -35591,7 +35591,7 @@
         <v>70.88619966292134</v>
       </c>
       <c r="C13" t="n">
-        <v>85.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>72.46378194444452</v>
@@ -35603,19 +35603,19 @@
         <v>83.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>113.1328484699454</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>130.8000870131355</v>
       </c>
       <c r="I13" t="n">
-        <v>4.526950216602403</v>
+        <v>186.6810361831604</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>335.2252478854037</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>90.01102947754548</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35648,16 +35648,16 @@
         <v>207.0512480698044</v>
       </c>
       <c r="V13" t="n">
-        <v>158.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>131.6271901612903</v>
+        <v>62.56512015788505</v>
       </c>
       <c r="X13" t="n">
-        <v>110.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>70.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>370.0000000000073</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>370.0000000000165</v>
+        <v>50.11444221105527</v>
       </c>
       <c r="L14" t="n">
-        <v>370.0000000000164</v>
+        <v>248.5697660962413</v>
       </c>
       <c r="M14" t="n">
-        <v>298.6842083072843</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35712,7 +35712,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35785,7 +35785,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O15" t="n">
-        <v>291.1959588280492</v>
+        <v>291.195958828044</v>
       </c>
       <c r="P15" t="n">
         <v>153.9181177222004</v>
@@ -35828,13 +35828,13 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>112.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>104.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -35876,25 +35876,25 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>25.70629078894784</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>175.7305154609554</v>
+        <v>34.78522282580784</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>185.8296897837838</v>
       </c>
       <c r="W16" t="n">
         <v>158.6271901612903</v>
       </c>
       <c r="X16" t="n">
-        <v>37.9752595651252</v>
+        <v>137.5563545698924</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>97.53464715053764</v>
       </c>
     </row>
     <row r="17">
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="K17" t="n">
-        <v>50.11444221105528</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L17" t="n">
-        <v>248.5697660962481</v>
+        <v>62.17139698492457</v>
       </c>
       <c r="M17" t="n">
-        <v>370.0000000000074</v>
+        <v>186.3983691113166</v>
       </c>
       <c r="N17" t="n">
-        <v>370.0000000000074</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -35949,10 +35949,10 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q17" t="n">
-        <v>370.0000000000074</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="R17" t="n">
-        <v>6.430770618596463e-12</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -36022,7 +36022,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O18" t="n">
-        <v>291.1959588280502</v>
+        <v>291.195958828044</v>
       </c>
       <c r="P18" t="n">
         <v>153.9181177222004</v>
@@ -36062,37 +36062,37 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>113.8861996629213</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>83.69251832732023</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>115.4637819444445</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>120.0190951630435</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>126.6171440322581</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>156.1328484699454</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>173.8000870131355</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>229.6810361831604</v>
       </c>
       <c r="J19" t="n">
-        <v>284.234753414531</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>133.0110294775455</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.726011186483124</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -36116,19 +36116,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>191.7305154609554</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>250.0512480698044</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>201.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>174.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>153.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>113.5346471505376</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>370.0000000000075</v>
       </c>
       <c r="K20" t="n">
-        <v>50.11444221105528</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L20" t="n">
-        <v>248.569766096241</v>
+        <v>62.17139698492457</v>
       </c>
       <c r="M20" t="n">
         <v>370.0000000000075</v>
       </c>
       <c r="N20" t="n">
-        <v>370.0000000000075</v>
+        <v>186.3983691113094</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -36189,7 +36189,7 @@
         <v>370.0000000000075</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>7.349452135538815e-12</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36259,7 +36259,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O21" t="n">
-        <v>291.1959588280566</v>
+        <v>291.195958828044</v>
       </c>
       <c r="P21" t="n">
         <v>153.9181177222004</v>
@@ -36299,10 +36299,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>97.24621361071674</v>
+        <v>113.8861996629213</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>128.2747533519553</v>
       </c>
       <c r="D22" t="n">
         <v>115.4637819444445</v>
@@ -36317,19 +36317,19 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>173.8000870131355</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>229.6810361831604</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>370.0000000000075</v>
       </c>
       <c r="K22" t="n">
-        <v>133.0110294775455</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>3.726011186483124</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -36359,13 +36359,13 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>67.11987972498177</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>174.6271901612903</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>153.5563545698924</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>370.0000000000077</v>
       </c>
       <c r="K23" t="n">
-        <v>50.11444221105528</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L23" t="n">
-        <v>370.0000000000164</v>
+        <v>62.17139698492457</v>
       </c>
       <c r="M23" t="n">
-        <v>370.0000000000088</v>
+        <v>370.0000000000077</v>
       </c>
       <c r="N23" t="n">
-        <v>248.5697660962429</v>
+        <v>370.0000000000077</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36423,10 +36423,10 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q23" t="n">
-        <v>370.0000000000088</v>
+        <v>186.3983691113096</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.430770618596463e-12</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36496,7 +36496,7 @@
         <v>189.4501538822398</v>
       </c>
       <c r="O24" t="n">
-        <v>291.1959588280566</v>
+        <v>291.195958828044</v>
       </c>
       <c r="P24" t="n">
         <v>153.9181177222004</v>
@@ -36536,13 +36536,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>101.0542763282298</v>
+        <v>113.8861996629213</v>
       </c>
       <c r="C25" t="n">
         <v>128.2747533519553</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>115.4637819444445</v>
       </c>
       <c r="E25" t="n">
         <v>120.0190951630435</v>
@@ -36551,10 +36551,10 @@
         <v>126.6171440322581</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>156.1328484699454</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>173.8000870131355</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -36563,10 +36563,10 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>133.0110294775455</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.726011186483124</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -36587,22 +36587,22 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>41.70629078894784</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>250.0512480698044</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>201.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>174.6271901612903</v>
+        <v>143.3925103695774</v>
       </c>
       <c r="X25" t="n">
-        <v>153.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>113.5346471505376</v>
@@ -36645,22 +36645,22 @@
         <v>50.11444221105528</v>
       </c>
       <c r="L26" t="n">
-        <v>62.17139698492463</v>
+        <v>218.8222913487656</v>
       </c>
       <c r="M26" t="n">
-        <v>339.0000000000242</v>
+        <v>339.000000000011</v>
       </c>
       <c r="N26" t="n">
-        <v>156.6508943638618</v>
+        <v>339.000000000011</v>
       </c>
       <c r="O26" t="n">
-        <v>339.0000000000242</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>56.36629674323819</v>
       </c>
       <c r="Q26" t="n">
-        <v>339.0000000000242</v>
+        <v>339.000000000011</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,7 +36718,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>21.96244577405877</v>
+        <v>145.1238703886191</v>
       </c>
       <c r="K27" t="n">
         <v>225.1422131313574</v>
@@ -36736,7 +36736,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P27" t="n">
-        <v>153.9181177222004</v>
+        <v>30.75669310757982</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>339.0000000000138</v>
+        <v>339.0000000000092</v>
       </c>
       <c r="K29" t="n">
-        <v>206.7653365748911</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L29" t="n">
         <v>62.17139698492463</v>
       </c>
       <c r="M29" t="n">
-        <v>339.0000000000138</v>
+        <v>339.0000000000092</v>
       </c>
       <c r="N29" t="n">
-        <v>339.0000000000138</v>
+        <v>156.6508943638427</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36897,7 +36897,7 @@
         <v>56.36629674323819</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>339.0000000000092</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36973,7 +36973,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P30" t="n">
-        <v>30.75669310758304</v>
+        <v>30.75669310757615</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -37116,25 +37116,25 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>50.11444221105527</v>
+        <v>50.11444221105528</v>
       </c>
       <c r="L32" t="n">
-        <v>202.5091600356211</v>
+        <v>62.17139698492463</v>
       </c>
       <c r="M32" t="n">
-        <v>322.0000000000164</v>
+        <v>322.0000000000132</v>
       </c>
       <c r="N32" t="n">
-        <v>322.0000000000164</v>
+        <v>322.0000000000132</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>322.0000000000132</v>
       </c>
       <c r="P32" t="n">
         <v>56.36629674323819</v>
       </c>
       <c r="Q32" t="n">
-        <v>322.0000000000164</v>
+        <v>140.3377630506938</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,13 +37192,13 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>145.1238703886191</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>225.1422131313574</v>
+        <v>179.791527592215</v>
       </c>
       <c r="L33" t="n">
-        <v>283.3037107280444</v>
+        <v>319.8601489335927</v>
       </c>
       <c r="M33" t="n">
         <v>140.3600421645043</v>
@@ -37210,7 +37210,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>153.9181177222004</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37247,34 +37247,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>131.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>146.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>133.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>138.0190951630435</v>
       </c>
       <c r="F34" t="n">
-        <v>144.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>174.1328484699454</v>
       </c>
       <c r="H34" t="n">
         <v>191.8000870131355</v>
       </c>
       <c r="I34" t="n">
-        <v>48.49348707055911</v>
+        <v>247.6810361831604</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>151.0110294775455</v>
       </c>
       <c r="L34" t="n">
         <v>21.72601118648312</v>
@@ -37298,10 +37298,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>59.70629078894784</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>143.7605157124316</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -37313,7 +37313,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>171.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>131.5346471505376</v>
@@ -37350,19 +37350,19 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>309</v>
-      </c>
-      <c r="K35" t="n">
-        <v>50.11444221105529</v>
       </c>
       <c r="L35" t="n">
         <v>62.17139698492463</v>
       </c>
       <c r="M35" t="n">
-        <v>127.8630155759332</v>
+        <v>309</v>
       </c>
       <c r="N35" t="n">
-        <v>309</v>
+        <v>177.9774577869885</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37429,13 +37429,13 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>145.1238703886191</v>
+        <v>67.95283364185099</v>
       </c>
       <c r="K36" t="n">
         <v>225.1422131313574</v>
       </c>
       <c r="L36" t="n">
-        <v>231.8289632532319</v>
+        <v>309</v>
       </c>
       <c r="M36" t="n">
         <v>140.3600421645043</v>
@@ -37487,34 +37487,34 @@
         <v>137.8861996629213</v>
       </c>
       <c r="C37" t="n">
-        <v>152.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>139.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>144.0190951630435</v>
       </c>
       <c r="F37" t="n">
-        <v>150.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>197.8000870131355</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>170.5474012488562</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>157.0110294775455</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>27.72601118648311</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,25 +37535,25 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>65.70629078894785</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>274.0512480698043</v>
+        <v>214.6663697881615</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>198.6271901612903</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>137.5346471505376</v>
       </c>
     </row>
     <row r="38">
@@ -37587,16 +37587,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="K38" t="n">
-        <v>309</v>
+        <v>50.11444221105529</v>
       </c>
       <c r="L38" t="n">
         <v>62.17139698492463</v>
       </c>
       <c r="M38" t="n">
-        <v>177.9774577869885</v>
+        <v>127.8630155759332</v>
       </c>
       <c r="N38" t="n">
         <v>309</v>
@@ -37666,7 +37666,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>145.1238703886191</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>225.1422131313574</v>
@@ -37675,7 +37675,7 @@
         <v>309</v>
       </c>
       <c r="M39" t="n">
-        <v>63.189005417736</v>
+        <v>54.3947580841548</v>
       </c>
       <c r="N39" t="n">
         <v>189.4501538822398</v>
@@ -37684,7 +37684,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>153.9181177222004</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37733,10 +37733,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>97.28960299310525</v>
       </c>
       <c r="G40" t="n">
-        <v>30.93439714334326</v>
+        <v>180.1328484699454</v>
       </c>
       <c r="H40" t="n">
         <v>197.8000870131355</v>
@@ -37745,7 +37745,7 @@
         <v>253.6810361831604</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="K40" t="n">
         <v>157.0110294775455</v>
@@ -37772,13 +37772,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>65.70629078894784</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>215.7305154609554</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>274.0512480698043</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -37903,19 +37903,19 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>145.1238703886191</v>
       </c>
       <c r="K42" t="n">
         <v>225.1422131313574</v>
       </c>
       <c r="L42" t="n">
-        <v>309</v>
+        <v>267.3609994132713</v>
       </c>
       <c r="M42" t="n">
         <v>140.3600421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>103.4848698018904</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>291.6099086951992</v>
@@ -37982,7 +37982,7 @@
         <v>141.6810361831604</v>
       </c>
       <c r="J43" t="n">
-        <v>161.2995310204779</v>
+        <v>290.2252478854037</v>
       </c>
       <c r="K43" t="n">
         <v>45.01102947754548</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>103.7305154609554</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>162.0512480698044</v>
+        <v>136.8560466658341</v>
       </c>
       <c r="V43" t="n">
         <v>113.8296897837838</v>
@@ -38067,16 +38067,16 @@
         <v>50.11444221105528</v>
       </c>
       <c r="L44" t="n">
-        <v>190.0344125608579</v>
+        <v>62.17139698492461</v>
       </c>
       <c r="M44" t="n">
         <v>309</v>
       </c>
       <c r="N44" t="n">
+        <v>127.8630155759333</v>
+      </c>
+      <c r="O44" t="n">
         <v>309</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>56.36629674323819</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>145.1238703886191</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>225.1422131313574</v>
       </c>
       <c r="L45" t="n">
-        <v>231.8289632532319</v>
+        <v>309</v>
       </c>
       <c r="M45" t="n">
         <v>140.3600421645043</v>
@@ -38158,7 +38158,7 @@
         <v>291.6099086951992</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>67.95283364185087</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
